--- a/Doc/Arch/TeC命令表.xlsx
+++ b/Doc/Arch/TeC命令表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sigemura/sigemura/DOC/よく使うもの/20_GitHub/Org_TeC7new/TeC7/Doc/Arch/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sigemura/20_GitHub/TeC7/Doc/Arch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04554A30-C95F-2A4C-8C33-7E0F757B9FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AFF8C7-E24C-9F41-BCB1-B51B9B1FB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="500" windowWidth="25120" windowHeight="15000" xr2:uid="{68F70C4F-7FF3-B64E-A555-E2BFC8105214}"/>
+    <workbookView xWindow="420" yWindow="600" windowWidth="25120" windowHeight="15000" activeTab="1" xr2:uid="{68F70C4F-7FF3-B64E-A555-E2BFC8105214}"/>
   </bookViews>
   <sheets>
     <sheet name="教科書掲載用" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="282">
   <si>
     <t>OP</t>
     <phoneticPr fontId="1"/>
@@ -1850,10 +1850,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Jump ou Carry</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Call subroutine</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1873,10 +1869,6 @@
   </si>
   <si>
     <t>　GR  ← [EA]</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　EA  ← [GR]</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -2179,10 +2171,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Ver.4.0(2025.1.24)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>SIO-Stat: b7:Tx Ready, b6:Rx Ready</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2326,6 +2314,22 @@
     <rPh sb="0" eb="2">
       <t>シュウキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ver.4.1(2026.1.19)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　[EA]  ← GR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GR ← GR &gt;&gt;&gt; 1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>◯</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3317,7 +3321,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3525,16 +3529,133 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3603,96 +3724,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3708,43 +3784,43 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3753,7 +3829,40 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
@@ -3765,121 +3874,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4218,71 +4213,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="17" customHeight="1">
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="112" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="73"/>
+      <c r="C1" s="112"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
     </row>
     <row r="2" spans="2:11" ht="17" customHeight="1" thickBot="1">
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
       <c r="D2" s="1"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
     </row>
     <row r="3" spans="2:11" s="4" customFormat="1" ht="16" customHeight="1">
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="131" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="C3" s="116" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="120" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="77" t="s">
+      <c r="E3" s="121"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="H3" s="86" t="s">
+      <c r="H3" s="125" t="s">
         <v>133</v>
       </c>
-      <c r="I3" s="87"/>
-      <c r="J3" s="94" t="s">
+      <c r="I3" s="126"/>
+      <c r="J3" s="133" t="s">
         <v>187</v>
       </c>
-      <c r="K3" s="77" t="s">
+      <c r="K3" s="116" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="4" spans="2:11" s="4" customFormat="1" ht="16" customHeight="1" thickBot="1">
-      <c r="B4" s="93"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="84" t="s">
+      <c r="B4" s="132"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="85"/>
+      <c r="E4" s="124"/>
       <c r="F4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="78"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="117"/>
     </row>
     <row r="5" spans="2:11" ht="16" customHeight="1">
       <c r="B5" s="6" t="s">
@@ -4291,20 +4286,20 @@
       <c r="C5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="79" t="s">
+      <c r="D5" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="80"/>
+      <c r="E5" s="119"/>
       <c r="F5" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="90" t="s">
+      <c r="H5" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="91"/>
+      <c r="I5" s="130"/>
       <c r="J5" s="8">
         <v>2</v>
       </c>
@@ -4319,20 +4314,20 @@
       <c r="C6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="70"/>
+      <c r="E6" s="109"/>
       <c r="F6" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="71" t="s">
+      <c r="H6" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="72"/>
+      <c r="I6" s="105"/>
       <c r="J6" s="12" t="s">
         <v>184</v>
       </c>
@@ -4347,20 +4342,20 @@
       <c r="C7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="70"/>
+      <c r="E7" s="109"/>
       <c r="F7" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="71" t="s">
+      <c r="H7" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="72"/>
+      <c r="I7" s="105"/>
       <c r="J7" s="14" t="s">
         <v>185</v>
       </c>
@@ -4375,20 +4370,20 @@
       <c r="C8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="70"/>
+      <c r="E8" s="109"/>
       <c r="F8" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="71" t="s">
+      <c r="H8" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I8" s="72"/>
+      <c r="I8" s="105"/>
       <c r="J8" s="12" t="s">
         <v>184</v>
       </c>
@@ -4403,20 +4398,20 @@
       <c r="C9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="70"/>
+      <c r="E9" s="109"/>
       <c r="F9" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="71" t="s">
+      <c r="H9" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I9" s="72"/>
+      <c r="I9" s="105"/>
       <c r="J9" s="12" t="s">
         <v>184</v>
       </c>
@@ -4431,20 +4426,20 @@
       <c r="C10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="D10" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="70"/>
+      <c r="E10" s="109"/>
       <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="71" t="s">
+      <c r="H10" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I10" s="72"/>
+      <c r="I10" s="105"/>
       <c r="J10" s="12" t="s">
         <v>184</v>
       </c>
@@ -4459,20 +4454,20 @@
       <c r="C11" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="70"/>
+      <c r="E11" s="109"/>
       <c r="F11" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="71" t="s">
+      <c r="H11" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I11" s="72"/>
+      <c r="I11" s="105"/>
       <c r="J11" s="12" t="s">
         <v>184</v>
       </c>
@@ -4487,20 +4482,20 @@
       <c r="C12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="D12" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="70"/>
+      <c r="E12" s="109"/>
       <c r="F12" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="71" t="s">
+      <c r="H12" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I12" s="72"/>
+      <c r="I12" s="105"/>
       <c r="J12" s="12" t="s">
         <v>184</v>
       </c>
@@ -4515,20 +4510,20 @@
       <c r="C13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="108" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="70"/>
+      <c r="E13" s="109"/>
       <c r="F13" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="71" t="s">
+      <c r="H13" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I13" s="72"/>
+      <c r="I13" s="105"/>
       <c r="J13" s="12" t="s">
         <v>184</v>
       </c>
@@ -4543,20 +4538,20 @@
       <c r="C14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="70"/>
+      <c r="E14" s="109"/>
       <c r="F14" s="11" t="s">
         <v>78</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="71" t="s">
+      <c r="H14" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I14" s="72"/>
+      <c r="I14" s="105"/>
       <c r="J14" s="11">
         <v>3</v>
       </c>
@@ -4571,20 +4566,20 @@
       <c r="C15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="70"/>
+      <c r="E15" s="109"/>
       <c r="F15" s="11" t="s">
         <v>79</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="71" t="s">
+      <c r="H15" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I15" s="72"/>
+      <c r="I15" s="105"/>
       <c r="J15" s="11">
         <v>3</v>
       </c>
@@ -4599,20 +4594,20 @@
       <c r="C16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="70"/>
+      <c r="E16" s="109"/>
       <c r="F16" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H16" s="71" t="s">
+      <c r="H16" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I16" s="72"/>
+      <c r="I16" s="105"/>
       <c r="J16" s="11">
         <v>3</v>
       </c>
@@ -4627,20 +4622,20 @@
       <c r="C17" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="69" t="s">
+      <c r="D17" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="E17" s="70"/>
+      <c r="E17" s="109"/>
       <c r="F17" s="11" t="s">
         <v>81</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="71" t="s">
+      <c r="H17" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I17" s="72"/>
+      <c r="I17" s="105"/>
       <c r="J17" s="11">
         <v>3</v>
       </c>
@@ -4655,20 +4650,20 @@
       <c r="C18" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="69" t="s">
+      <c r="D18" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="70"/>
+      <c r="E18" s="109"/>
       <c r="F18" s="11" t="s">
         <v>82</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="71" t="s">
+      <c r="H18" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I18" s="72"/>
+      <c r="I18" s="105"/>
       <c r="J18" s="14" t="s">
         <v>185</v>
       </c>
@@ -4683,20 +4678,20 @@
       <c r="C19" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="69" t="s">
+      <c r="D19" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="70"/>
+      <c r="E19" s="109"/>
       <c r="F19" s="11" t="s">
         <v>83</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="71" t="s">
+      <c r="H19" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="72"/>
+      <c r="I19" s="105"/>
       <c r="J19" s="14" t="s">
         <v>185</v>
       </c>
@@ -4711,20 +4706,20 @@
       <c r="C20" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="70"/>
+      <c r="E20" s="109"/>
       <c r="F20" s="11" t="s">
         <v>84</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H20" s="71" t="s">
+      <c r="H20" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="72"/>
+      <c r="I20" s="105"/>
       <c r="J20" s="14" t="s">
         <v>185</v>
       </c>
@@ -4739,20 +4734,20 @@
       <c r="C21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="69" t="s">
+      <c r="D21" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="70"/>
+      <c r="E21" s="109"/>
       <c r="F21" s="11" t="s">
         <v>85</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="71" t="s">
+      <c r="H21" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="72"/>
+      <c r="I21" s="105"/>
       <c r="J21" s="14" t="s">
         <v>185</v>
       </c>
@@ -4767,20 +4762,20 @@
       <c r="C22" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="70"/>
+      <c r="E22" s="109"/>
       <c r="F22" s="11" t="s">
         <v>82</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="71" t="s">
+      <c r="H22" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I22" s="72"/>
+      <c r="I22" s="105"/>
       <c r="J22" s="14" t="s">
         <v>184</v>
       </c>
@@ -4795,20 +4790,20 @@
       <c r="C23" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="69" t="s">
+      <c r="D23" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="70"/>
+      <c r="E23" s="109"/>
       <c r="F23" s="11" t="s">
         <v>83</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="71" t="s">
+      <c r="H23" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I23" s="72"/>
+      <c r="I23" s="105"/>
       <c r="J23" s="14" t="s">
         <v>185</v>
       </c>
@@ -4823,20 +4818,20 @@
       <c r="C24" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="69" t="s">
+      <c r="D24" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="70"/>
+      <c r="E24" s="109"/>
       <c r="F24" s="11" t="s">
         <v>84</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="71" t="s">
+      <c r="H24" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I24" s="72"/>
+      <c r="I24" s="105"/>
       <c r="J24" s="14" t="s">
         <v>185</v>
       </c>
@@ -4851,20 +4846,20 @@
       <c r="C25" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="D25" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="70"/>
+      <c r="E25" s="109"/>
       <c r="F25" s="11" t="s">
         <v>85</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="71" t="s">
+      <c r="H25" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="72"/>
+      <c r="I25" s="105"/>
       <c r="J25" s="14" t="s">
         <v>185</v>
       </c>
@@ -4879,20 +4874,20 @@
       <c r="C26" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="69" t="s">
+      <c r="D26" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="E26" s="70"/>
+      <c r="E26" s="109"/>
       <c r="F26" s="11" t="s">
         <v>78</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="H26" s="71" t="s">
+      <c r="H26" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I26" s="72"/>
+      <c r="I26" s="105"/>
       <c r="J26" s="11">
         <v>4</v>
       </c>
@@ -4907,20 +4902,20 @@
       <c r="C27" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="69" t="s">
+      <c r="D27" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="70"/>
+      <c r="E27" s="109"/>
       <c r="F27" s="11" t="s">
         <v>81</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="71" t="s">
+      <c r="H27" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I27" s="72"/>
+      <c r="I27" s="105"/>
       <c r="J27" s="11">
         <v>3</v>
       </c>
@@ -4935,20 +4930,20 @@
       <c r="C28" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="69" t="s">
+      <c r="D28" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="E28" s="70"/>
+      <c r="E28" s="109"/>
       <c r="F28" s="11" t="s">
         <v>78</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H28" s="71" t="s">
+      <c r="H28" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I28" s="72"/>
+      <c r="I28" s="105"/>
       <c r="J28" s="11">
         <v>3</v>
       </c>
@@ -4963,20 +4958,20 @@
       <c r="C29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="69" t="s">
+      <c r="D29" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="70"/>
+      <c r="E29" s="109"/>
       <c r="F29" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H29" s="71" t="s">
+      <c r="H29" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I29" s="72"/>
+      <c r="I29" s="105"/>
       <c r="J29" s="11">
         <v>4</v>
       </c>
@@ -4991,20 +4986,20 @@
       <c r="C30" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="69" t="s">
+      <c r="D30" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="70"/>
+      <c r="E30" s="109"/>
       <c r="F30" s="14" t="s">
         <v>34</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="71" t="s">
+      <c r="H30" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I30" s="72"/>
+      <c r="I30" s="105"/>
       <c r="J30" s="11">
         <v>3</v>
       </c>
@@ -5019,20 +5014,20 @@
       <c r="C31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="69" t="s">
+      <c r="D31" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="70"/>
+      <c r="E31" s="109"/>
       <c r="F31" s="14" t="s">
         <v>92</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H31" s="71" t="s">
+      <c r="H31" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="72"/>
+      <c r="I31" s="105"/>
       <c r="J31" s="11">
         <v>3</v>
       </c>
@@ -5047,20 +5042,20 @@
       <c r="C32" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="69" t="s">
+      <c r="D32" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="E32" s="70"/>
+      <c r="E32" s="109"/>
       <c r="F32" s="14" t="s">
         <v>93</v>
       </c>
       <c r="G32" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="71" t="s">
+      <c r="H32" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="I32" s="72"/>
+      <c r="I32" s="105"/>
       <c r="J32" s="11">
         <v>3</v>
       </c>
@@ -5075,20 +5070,20 @@
       <c r="C33" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="69" t="s">
+      <c r="D33" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="E33" s="70"/>
+      <c r="E33" s="109"/>
       <c r="F33" s="38" t="s">
         <v>89</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="104" t="s">
+      <c r="H33" s="106" t="s">
         <v>186</v>
       </c>
-      <c r="I33" s="105"/>
+      <c r="I33" s="107"/>
       <c r="J33" s="37">
         <v>4</v>
       </c>
@@ -5103,20 +5098,20 @@
       <c r="C34" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D34" s="98" t="s">
+      <c r="D34" s="110" t="s">
         <v>94</v>
       </c>
-      <c r="E34" s="99"/>
+      <c r="E34" s="111"/>
       <c r="F34" s="17" t="s">
         <v>89</v>
       </c>
       <c r="G34" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="106" t="s">
+      <c r="H34" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="I34" s="107"/>
+      <c r="I34" s="98"/>
       <c r="J34" s="18">
         <v>3</v>
       </c>
@@ -5133,17 +5128,17 @@
         <v>163</v>
       </c>
       <c r="D36" s="21"/>
-      <c r="E36" s="95" t="s">
+      <c r="E36" s="99" t="s">
         <v>164</v>
       </c>
-      <c r="F36" s="96"/>
-      <c r="G36" s="97"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="101"/>
       <c r="H36" s="21"/>
-      <c r="I36" s="95" t="s">
+      <c r="I36" s="99" t="s">
         <v>165</v>
       </c>
-      <c r="J36" s="96"/>
-      <c r="K36" s="97"/>
+      <c r="J36" s="100"/>
+      <c r="K36" s="101"/>
     </row>
     <row r="37" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B37" s="23" t="s">
@@ -5155,18 +5150,18 @@
       <c r="E37" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="F37" s="95" t="s">
+      <c r="F37" s="99" t="s">
         <v>166</v>
       </c>
-      <c r="G37" s="97"/>
+      <c r="G37" s="101"/>
       <c r="H37" s="21"/>
       <c r="I37" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="J37" s="95" t="s">
+      <c r="J37" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="K37" s="97"/>
+      <c r="K37" s="101"/>
     </row>
     <row r="38" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="B38" s="25" t="s">
@@ -5201,16 +5196,16 @@
       <c r="E39" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="F39" s="100"/>
-      <c r="G39" s="101"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="90"/>
       <c r="H39" s="21"/>
       <c r="I39" s="30">
         <v>1</v>
       </c>
-      <c r="J39" s="100" t="s">
+      <c r="J39" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="K39" s="101"/>
+      <c r="K39" s="90"/>
     </row>
     <row r="40" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B40" s="31" t="s">
@@ -5222,34 +5217,34 @@
       <c r="E40" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="100"/>
-      <c r="G40" s="101"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="90"/>
       <c r="H40" s="21"/>
       <c r="I40" s="30">
         <v>2</v>
       </c>
-      <c r="J40" s="100" t="s">
+      <c r="J40" s="89" t="s">
         <v>122</v>
       </c>
-      <c r="K40" s="101"/>
+      <c r="K40" s="90"/>
     </row>
     <row r="41" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B41" s="21"/>
       <c r="E41" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="F41" s="100" t="s">
+      <c r="F41" s="89" t="s">
         <v>167</v>
       </c>
-      <c r="G41" s="101"/>
+      <c r="G41" s="90"/>
       <c r="H41" s="21"/>
       <c r="I41" s="30">
         <v>3</v>
       </c>
-      <c r="J41" s="100" t="s">
+      <c r="J41" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="K41" s="101"/>
+      <c r="K41" s="90"/>
     </row>
     <row r="42" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B42" s="20" t="s">
@@ -5262,18 +5257,18 @@
       <c r="E42" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="F42" s="100" t="s">
+      <c r="F42" s="89" t="s">
         <v>168</v>
       </c>
-      <c r="G42" s="101"/>
+      <c r="G42" s="90"/>
       <c r="H42" s="21"/>
       <c r="I42" s="30">
         <v>4</v>
       </c>
-      <c r="J42" s="100" t="s">
+      <c r="J42" s="89" t="s">
         <v>169</v>
       </c>
-      <c r="K42" s="101"/>
+      <c r="K42" s="90"/>
     </row>
     <row r="43" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="B43" s="23" t="s">
@@ -5285,18 +5280,18 @@
       <c r="E43" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="F43" s="100" t="s">
+      <c r="F43" s="89" t="s">
         <v>171</v>
       </c>
-      <c r="G43" s="101"/>
+      <c r="G43" s="90"/>
       <c r="H43" s="21"/>
       <c r="I43" s="30">
         <v>5</v>
       </c>
-      <c r="J43" s="100" t="s">
+      <c r="J43" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="K43" s="101"/>
+      <c r="K43" s="90"/>
     </row>
     <row r="44" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="B44" s="25" t="s">
@@ -5308,18 +5303,18 @@
       <c r="E44" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="F44" s="100" t="s">
+      <c r="F44" s="89" t="s">
         <v>173</v>
       </c>
-      <c r="G44" s="101"/>
+      <c r="G44" s="90"/>
       <c r="H44" s="21"/>
       <c r="I44" s="30">
         <v>6</v>
       </c>
-      <c r="J44" s="100" t="s">
+      <c r="J44" s="89" t="s">
         <v>174</v>
       </c>
-      <c r="K44" s="101"/>
+      <c r="K44" s="90"/>
     </row>
     <row r="45" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="B45" s="25" t="s">
@@ -5331,18 +5326,18 @@
       <c r="E45" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="F45" s="100" t="s">
+      <c r="F45" s="89" t="s">
         <v>176</v>
       </c>
-      <c r="G45" s="101"/>
+      <c r="G45" s="90"/>
       <c r="H45" s="21"/>
       <c r="I45" s="30">
         <v>7</v>
       </c>
-      <c r="J45" s="100" t="s">
+      <c r="J45" s="89" t="s">
         <v>126</v>
       </c>
-      <c r="K45" s="101"/>
+      <c r="K45" s="90"/>
     </row>
     <row r="46" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="B46" s="31" t="s">
@@ -5354,31 +5349,31 @@
       <c r="E46" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="F46" s="100"/>
-      <c r="G46" s="101"/>
+      <c r="F46" s="89"/>
+      <c r="G46" s="90"/>
       <c r="H46" s="21"/>
       <c r="I46" s="30">
         <v>8</v>
       </c>
-      <c r="J46" s="100" t="s">
+      <c r="J46" s="89" t="s">
         <v>178</v>
       </c>
-      <c r="K46" s="101"/>
+      <c r="K46" s="90"/>
     </row>
     <row r="47" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1" thickBot="1">
       <c r="E47" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="F47" s="112"/>
-      <c r="G47" s="113"/>
+      <c r="F47" s="95"/>
+      <c r="G47" s="96"/>
       <c r="H47" s="21"/>
       <c r="I47" s="30">
         <v>9</v>
       </c>
-      <c r="J47" s="100" t="s">
+      <c r="J47" s="89" t="s">
         <v>179</v>
       </c>
-      <c r="K47" s="101"/>
+      <c r="K47" s="90"/>
     </row>
     <row r="48" spans="2:11" s="22" customFormat="1" ht="15" customHeight="1">
       <c r="E48" s="21"/>
@@ -5388,88 +5383,88 @@
       <c r="I48" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="J48" s="100" t="s">
+      <c r="J48" s="89" t="s">
         <v>180</v>
       </c>
-      <c r="K48" s="101"/>
+      <c r="K48" s="90"/>
     </row>
     <row r="49" spans="2:11" s="22" customFormat="1" ht="20" customHeight="1">
-      <c r="B49" s="182" t="s">
-        <v>274</v>
-      </c>
-      <c r="C49" s="185"/>
-      <c r="D49" s="187"/>
-      <c r="E49" s="183" t="s">
-        <v>278</v>
-      </c>
-      <c r="F49" s="184"/>
-      <c r="G49" s="186"/>
+      <c r="B49" s="84" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="87"/>
+      <c r="D49" s="87"/>
+      <c r="E49" s="85" t="s">
+        <v>275</v>
+      </c>
+      <c r="F49" s="86"/>
+      <c r="G49" s="88"/>
       <c r="H49" s="21"/>
       <c r="I49" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="J49" s="100" t="s">
+      <c r="J49" s="89" t="s">
         <v>181</v>
       </c>
-      <c r="K49" s="101"/>
+      <c r="K49" s="90"/>
     </row>
     <row r="50" spans="2:11" s="22" customFormat="1" ht="18">
-      <c r="B50" s="182" t="s">
-        <v>275</v>
-      </c>
-      <c r="C50" s="185"/>
-      <c r="D50" s="185"/>
-      <c r="E50" s="183" t="s">
-        <v>279</v>
-      </c>
-      <c r="F50" s="187"/>
-      <c r="G50" s="187"/>
+      <c r="B50" s="84" t="s">
+        <v>272</v>
+      </c>
+      <c r="C50" s="87"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="85" t="s">
+        <v>276</v>
+      </c>
+      <c r="F50" s="87"/>
+      <c r="G50" s="87"/>
       <c r="H50" s="21"/>
       <c r="I50" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="J50" s="100" t="s">
+      <c r="J50" s="89" t="s">
         <v>182</v>
       </c>
-      <c r="K50" s="101"/>
+      <c r="K50" s="90"/>
     </row>
     <row r="51" spans="2:11" s="22" customFormat="1">
-      <c r="B51" s="182" t="s">
-        <v>276</v>
-      </c>
-      <c r="C51" s="185"/>
-      <c r="D51" s="185"/>
-      <c r="E51" s="183" t="s">
-        <v>280</v>
-      </c>
-      <c r="F51" s="187"/>
-      <c r="G51" s="187"/>
+      <c r="B51" s="84" t="s">
+        <v>273</v>
+      </c>
+      <c r="C51" s="87"/>
+      <c r="D51" s="87"/>
+      <c r="E51" s="85" t="s">
+        <v>277</v>
+      </c>
+      <c r="F51" s="87"/>
+      <c r="G51" s="87"/>
       <c r="H51" s="21"/>
       <c r="I51" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="J51" s="108" t="s">
+      <c r="J51" s="91" t="s">
         <v>183</v>
       </c>
-      <c r="K51" s="109"/>
+      <c r="K51" s="92"/>
     </row>
     <row r="52" spans="2:11" s="22" customFormat="1" ht="16" thickBot="1">
-      <c r="B52" s="182" t="s">
-        <v>277</v>
-      </c>
-      <c r="C52" s="185"/>
-      <c r="D52" s="185"/>
-      <c r="E52" s="183" t="s">
+      <c r="B52" s="84" t="s">
+        <v>274</v>
+      </c>
+      <c r="C52" s="87"/>
+      <c r="D52" s="87"/>
+      <c r="E52" s="85" t="s">
         <v>127</v>
       </c>
-      <c r="F52" s="187"/>
-      <c r="G52" s="187"/>
+      <c r="F52" s="87"/>
+      <c r="G52" s="87"/>
       <c r="H52" s="21"/>
       <c r="I52" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="J52" s="110"/>
-      <c r="K52" s="111"/>
+      <c r="J52" s="93"/>
+      <c r="K52" s="94"/>
     </row>
     <row r="53" spans="2:11" s="22" customFormat="1">
       <c r="C53" s="3"/>
@@ -5484,64 +5479,27 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="J51:K52"/>
-    <mergeCell ref="F45:G47"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="F38:G40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="H8:I8"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="B1:C2"/>
@@ -5558,27 +5516,64 @@
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J51:K52"/>
+    <mergeCell ref="F45:G47"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F38:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J50:K50"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5616,190 +5611,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" s="155"/>
-      <c r="B1" s="156"/>
-      <c r="W1" s="155"/>
-      <c r="X1" s="156"/>
+      <c r="A1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="W1" s="70"/>
+      <c r="X1" s="71"/>
     </row>
     <row r="2" spans="1:24">
-      <c r="A2" s="157"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="158"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="1:24" ht="20" customHeight="1">
-      <c r="A3" s="138"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="145" t="s">
-        <v>250</v>
-      </c>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="138"/>
-      <c r="O3" s="138"/>
-      <c r="P3" s="138"/>
-      <c r="Q3" s="138"/>
-      <c r="R3" s="138"/>
-      <c r="S3" s="138"/>
-      <c r="T3" s="138"/>
-      <c r="U3" s="138"/>
-      <c r="V3" s="138"/>
-      <c r="W3" s="138"/>
+      <c r="J3" s="138" t="s">
+        <v>248</v>
+      </c>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
     </row>
     <row r="4" spans="1:24" ht="20" customHeight="1">
-      <c r="B4" s="138"/>
-      <c r="C4" s="138" t="s">
-        <v>263</v>
-      </c>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="145"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="138"/>
-      <c r="R4" s="138"/>
-      <c r="S4" s="138"/>
-      <c r="T4" s="138"/>
-      <c r="U4" s="138"/>
-      <c r="V4" s="138"/>
-      <c r="W4" s="138"/>
+      <c r="C4" t="s">
+        <v>278</v>
+      </c>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
     </row>
     <row r="5" spans="1:24" ht="20" customHeight="1">
-      <c r="B5" s="138"/>
       <c r="C5" s="134" t="s">
         <v>189</v>
       </c>
       <c r="D5" s="134" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="131" t="s">
+      <c r="E5" s="136" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="133"/>
+      <c r="F5" s="137"/>
       <c r="G5" s="134" t="s">
         <v>192</v>
       </c>
       <c r="H5" s="134" t="s">
         <v>193</v>
       </c>
-      <c r="I5" s="124" t="s">
+      <c r="I5" s="139" t="s">
         <v>187</v>
       </c>
       <c r="J5" s="134" t="s">
         <v>194</v>
       </c>
-      <c r="K5" s="138"/>
       <c r="L5" s="134" t="s">
         <v>189</v>
       </c>
       <c r="M5" s="134" t="s">
         <v>190</v>
       </c>
-      <c r="N5" s="131" t="s">
+      <c r="N5" s="136" t="s">
         <v>191</v>
       </c>
-      <c r="O5" s="132"/>
-      <c r="P5" s="133"/>
+      <c r="O5" s="154"/>
+      <c r="P5" s="137"/>
       <c r="Q5" s="134" t="s">
         <v>192</v>
       </c>
-      <c r="R5" s="124" t="s">
+      <c r="R5" s="139" t="s">
         <v>193</v>
       </c>
-      <c r="S5" s="125"/>
-      <c r="T5" s="126"/>
+      <c r="S5" s="149"/>
+      <c r="T5" s="150"/>
       <c r="U5" s="134" t="s">
         <v>187</v>
       </c>
       <c r="V5" s="134" t="s">
         <v>194</v>
       </c>
-      <c r="W5" s="138"/>
     </row>
     <row r="6" spans="1:24">
-      <c r="B6" s="138"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="160" t="s">
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="161" t="s">
+      <c r="F6" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="166" t="s">
+      <c r="G6" s="135"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="135"/>
+      <c r="L6" s="135"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="O6" s="167"/>
-      <c r="P6" s="161" t="s">
+      <c r="O6" s="147"/>
+      <c r="P6" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="Q6" s="135"/>
-      <c r="R6" s="127"/>
-      <c r="S6" s="128"/>
-      <c r="T6" s="129"/>
-      <c r="U6" s="135"/>
-      <c r="V6" s="135"/>
-      <c r="W6" s="138"/>
+      <c r="Q6" s="148"/>
+      <c r="R6" s="151"/>
+      <c r="S6" s="152"/>
+      <c r="T6" s="153"/>
+      <c r="U6" s="148"/>
+      <c r="V6" s="148"/>
     </row>
     <row r="7" spans="1:24">
-      <c r="B7" s="138"/>
       <c r="C7" s="43" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="E7" s="162" t="s">
+      <c r="E7" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="163" t="s">
+      <c r="F7" s="78" t="s">
         <v>34</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H7" s="50" t="s">
         <v>36</v>
@@ -5808,50 +5740,47 @@
         <v>2</v>
       </c>
       <c r="J7" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="K7" s="138"/>
+        <v>199</v>
+      </c>
       <c r="L7" s="55" t="s">
         <v>26</v>
       </c>
       <c r="M7" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="N7" s="168" t="s">
+      <c r="N7" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="O7" s="169"/>
-      <c r="P7" s="170" t="s">
+      <c r="O7" s="145"/>
+      <c r="P7" s="81" t="s">
         <v>34</v>
       </c>
       <c r="Q7" s="61" t="s">
-        <v>249</v>
-      </c>
-      <c r="R7" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R7" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="123"/>
-      <c r="T7" s="122"/>
+      <c r="S7" s="142"/>
+      <c r="T7" s="143"/>
       <c r="U7" s="45">
         <v>3</v>
       </c>
       <c r="V7" s="41" t="s">
-        <v>221</v>
-      </c>
-      <c r="W7" s="138"/>
+        <v>219</v>
+      </c>
     </row>
     <row r="8" spans="1:24">
-      <c r="B8" s="138"/>
       <c r="C8" s="41" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="162" t="s">
-        <v>198</v>
-      </c>
-      <c r="F8" s="164" t="s">
+      <c r="E8" s="77" t="s">
+        <v>197</v>
+      </c>
+      <c r="F8" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G8" s="46" t="s">
@@ -5864,50 +5793,47 @@
         <v>4</v>
       </c>
       <c r="J8" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="K8" s="138"/>
+        <v>200</v>
+      </c>
       <c r="L8" s="60" t="s">
         <v>27</v>
       </c>
       <c r="M8" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="N8" s="171" t="s">
+      <c r="N8" s="157" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="172"/>
-      <c r="P8" s="163" t="s">
+      <c r="O8" s="158"/>
+      <c r="P8" s="78" t="s">
         <v>92</v>
       </c>
       <c r="Q8" s="49" t="s">
-        <v>249</v>
-      </c>
-      <c r="R8" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R8" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="S8" s="123"/>
-      <c r="T8" s="122"/>
+      <c r="S8" s="142"/>
+      <c r="T8" s="143"/>
       <c r="U8" s="46">
         <v>3</v>
       </c>
       <c r="V8" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="W8" s="138"/>
+        <v>220</v>
+      </c>
     </row>
     <row r="9" spans="1:24">
-      <c r="B9" s="138"/>
       <c r="C9" s="43" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="162" t="s">
+      <c r="E9" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="165" t="s">
+      <c r="F9" s="80" t="s">
         <v>66</v>
       </c>
       <c r="G9" s="45" t="s">
@@ -5920,153 +5846,144 @@
         <v>3</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="K9" s="138"/>
+        <v>279</v>
+      </c>
       <c r="L9" s="55" t="s">
         <v>28</v>
       </c>
       <c r="M9" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="N9" s="168" t="s">
+      <c r="N9" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="O9" s="169"/>
-      <c r="P9" s="170" t="s">
+      <c r="O9" s="145"/>
+      <c r="P9" s="81" t="s">
         <v>93</v>
       </c>
       <c r="Q9" s="61" t="s">
-        <v>249</v>
-      </c>
-      <c r="R9" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R9" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="123"/>
-      <c r="T9" s="122"/>
+      <c r="S9" s="142"/>
+      <c r="T9" s="143"/>
       <c r="U9" s="45">
         <v>3</v>
       </c>
       <c r="V9" s="41" t="s">
-        <v>223</v>
-      </c>
-      <c r="W9" s="138"/>
+        <v>221</v>
+      </c>
     </row>
     <row r="10" spans="1:24">
-      <c r="B10" s="138"/>
       <c r="C10" s="41" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="162" t="s">
+      <c r="E10" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="164" t="s">
+      <c r="F10" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G10" s="46" t="s">
         <v>35</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I10" s="45">
         <v>4</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>203</v>
-      </c>
-      <c r="K10" s="138"/>
-      <c r="L10" s="140" t="s">
+        <v>201</v>
+      </c>
+      <c r="L10" s="155" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="140" t="s">
-        <v>220</v>
-      </c>
-      <c r="N10" s="173" t="s">
+      <c r="M10" s="155" t="s">
+        <v>218</v>
+      </c>
+      <c r="N10" s="171" t="s">
         <v>91</v>
       </c>
-      <c r="O10" s="174"/>
-      <c r="P10" s="175" t="s">
+      <c r="O10" s="172"/>
+      <c r="P10" s="169" t="s">
         <v>89</v>
       </c>
-      <c r="Q10" s="143" t="s">
-        <v>249</v>
-      </c>
-      <c r="R10" s="116" t="s">
-        <v>36</v>
-      </c>
-      <c r="S10" s="117"/>
-      <c r="T10" s="118"/>
-      <c r="U10" s="140">
+      <c r="Q10" s="167" t="s">
+        <v>247</v>
+      </c>
+      <c r="R10" s="161" t="s">
+        <v>281</v>
+      </c>
+      <c r="S10" s="162"/>
+      <c r="T10" s="163"/>
+      <c r="U10" s="155">
         <v>4</v>
       </c>
-      <c r="V10" s="153" t="s">
-        <v>262</v>
-      </c>
-      <c r="W10" s="138"/>
+      <c r="V10" s="159" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="11" spans="1:24">
-      <c r="B11" s="138"/>
       <c r="C11" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="162" t="s">
+      <c r="E11" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="165" t="s">
+      <c r="F11" s="80" t="s">
         <v>66</v>
       </c>
       <c r="G11" s="45" t="s">
         <v>35</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I11" s="46">
         <v>4</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>204</v>
-      </c>
-      <c r="K11" s="138"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="176"/>
-      <c r="O11" s="177"/>
-      <c r="P11" s="178"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="120"/>
-      <c r="S11" s="130"/>
-      <c r="T11" s="115"/>
-      <c r="U11" s="141"/>
-      <c r="V11" s="154"/>
-      <c r="W11" s="138"/>
+        <v>202</v>
+      </c>
+      <c r="L11" s="156"/>
+      <c r="M11" s="156"/>
+      <c r="N11" s="173"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="170"/>
+      <c r="Q11" s="168"/>
+      <c r="R11" s="164"/>
+      <c r="S11" s="165"/>
+      <c r="T11" s="166"/>
+      <c r="U11" s="156"/>
+      <c r="V11" s="160"/>
     </row>
     <row r="12" spans="1:24">
-      <c r="B12" s="138"/>
       <c r="C12" s="41" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="162" t="s">
+      <c r="E12" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="164" t="s">
+      <c r="F12" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G12" s="46" t="s">
         <v>35</v>
       </c>
       <c r="H12" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I12" s="46">
         <v>4</v>
@@ -6074,151 +5991,130 @@
       <c r="J12" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="K12" s="138"/>
       <c r="L12" s="56" t="s">
         <v>30</v>
       </c>
       <c r="M12" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="N12" s="168" t="s">
+      <c r="N12" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="O12" s="169"/>
-      <c r="P12" s="179" t="s">
+      <c r="O12" s="145"/>
+      <c r="P12" s="82" t="s">
         <v>89</v>
       </c>
       <c r="Q12" s="59" t="s">
-        <v>249</v>
-      </c>
-      <c r="R12" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R12" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="S12" s="123"/>
-      <c r="T12" s="122"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="143"/>
       <c r="U12" s="48">
         <v>3</v>
       </c>
       <c r="V12" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="W12" s="138"/>
+        <v>222</v>
+      </c>
     </row>
     <row r="13" spans="1:24">
-      <c r="B13" s="138"/>
       <c r="C13" s="43" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="162" t="s">
+      <c r="E13" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="164" t="s">
+      <c r="F13" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G13" s="45" t="s">
         <v>35</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I13" s="46">
         <v>4</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>205</v>
-      </c>
-      <c r="K13" s="138"/>
-      <c r="L13" s="138"/>
-      <c r="M13" s="138"/>
-      <c r="N13" s="138"/>
-      <c r="O13" s="138"/>
-      <c r="P13" s="138"/>
-      <c r="Q13" s="138"/>
-      <c r="R13" s="138"/>
-      <c r="S13" s="138"/>
-      <c r="T13" s="138"/>
-      <c r="U13" s="138"/>
-      <c r="V13" s="138"/>
-      <c r="W13" s="138"/>
+        <v>203</v>
+      </c>
     </row>
     <row r="14" spans="1:24">
-      <c r="B14" s="138"/>
       <c r="C14" s="41" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="162" t="s">
+      <c r="E14" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="165" t="s">
+      <c r="F14" s="80" t="s">
         <v>66</v>
       </c>
       <c r="G14" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="139" t="s">
-        <v>199</v>
+      <c r="H14" s="69" t="s">
+        <v>198</v>
       </c>
       <c r="I14" s="45">
         <v>4</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>206</v>
-      </c>
-      <c r="K14" s="138"/>
+        <v>204</v>
+      </c>
       <c r="L14" s="46" t="s">
         <v>69</v>
       </c>
       <c r="M14" s="65" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N14" s="67"/>
-      <c r="O14" s="121" t="s">
-        <v>231</v>
-      </c>
-      <c r="P14" s="123"/>
-      <c r="Q14" s="123"/>
-      <c r="R14" s="122"/>
-      <c r="S14" s="139"/>
-      <c r="T14" s="121" t="s">
-        <v>238</v>
-      </c>
-      <c r="U14" s="123"/>
-      <c r="V14" s="122"/>
-      <c r="W14" s="138"/>
+      <c r="O14" s="141" t="s">
+        <v>229</v>
+      </c>
+      <c r="P14" s="142"/>
+      <c r="Q14" s="142"/>
+      <c r="R14" s="143"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="141" t="s">
+        <v>236</v>
+      </c>
+      <c r="U14" s="142"/>
+      <c r="V14" s="143"/>
     </row>
     <row r="15" spans="1:24">
-      <c r="B15" s="138"/>
       <c r="C15" s="43" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="162" t="s">
+      <c r="E15" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="164" t="s">
+      <c r="F15" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G15" s="46" t="s">
         <v>35</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I15" s="46">
         <v>4</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="K15" s="138"/>
+        <v>205</v>
+      </c>
       <c r="L15" s="44" t="s">
         <v>97</v>
       </c>
@@ -6229,48 +6125,45 @@
       <c r="O15" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="P15" s="121" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q15" s="123"/>
-      <c r="R15" s="122"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="121" t="s">
+      <c r="P15" s="141" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q15" s="142"/>
+      <c r="R15" s="143"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="U15" s="122"/>
+      <c r="U15" s="143"/>
       <c r="V15" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="W15" s="138"/>
     </row>
     <row r="16" spans="1:24">
-      <c r="B16" s="138"/>
       <c r="C16" s="43" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="162" t="s">
+      <c r="E16" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="164" t="s">
+      <c r="F16" s="79" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H16" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I16" s="46">
         <v>3</v>
       </c>
       <c r="J16" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="K16" s="138"/>
+        <v>206</v>
+      </c>
       <c r="L16" s="57" t="s">
         <v>98</v>
       </c>
@@ -6281,48 +6174,45 @@
       <c r="O16" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="P16" s="116" t="s">
+      <c r="P16" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="Q16" s="117"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="139"/>
-      <c r="T16" s="121">
+      <c r="Q16" s="162"/>
+      <c r="R16" s="163"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="141">
         <v>0</v>
       </c>
-      <c r="U16" s="122"/>
+      <c r="U16" s="143"/>
       <c r="V16" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="W16" s="138"/>
-    </row>
-    <row r="17" spans="2:23">
-      <c r="B17" s="138"/>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="3:22">
       <c r="C17" s="41" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="162" t="s">
+      <c r="E17" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="164" t="s">
+      <c r="F17" s="79" t="s">
         <v>79</v>
       </c>
       <c r="G17" s="46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I17" s="45">
         <v>3</v>
       </c>
       <c r="J17" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="K17" s="138"/>
+        <v>206</v>
+      </c>
       <c r="L17" s="44" t="s">
         <v>99</v>
       </c>
@@ -6333,46 +6223,43 @@
       <c r="O17" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="P17" s="119"/>
-      <c r="Q17" s="142"/>
-      <c r="R17" s="114"/>
-      <c r="S17" s="139"/>
-      <c r="T17" s="121">
+      <c r="P17" s="175"/>
+      <c r="Q17" s="176"/>
+      <c r="R17" s="177"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="141">
         <v>1</v>
       </c>
-      <c r="U17" s="122"/>
+      <c r="U17" s="143"/>
       <c r="V17" s="67" t="s">
-        <v>271</v>
-      </c>
-      <c r="W17" s="138"/>
-    </row>
-    <row r="18" spans="2:23">
-      <c r="B18" s="138"/>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22">
       <c r="C18" s="43" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="162" t="s">
+      <c r="E18" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="164" t="s">
+      <c r="F18" s="79" t="s">
         <v>80</v>
       </c>
       <c r="G18" s="46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H18" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I18" s="46">
         <v>3</v>
       </c>
       <c r="J18" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="K18" s="138"/>
+        <v>207</v>
+      </c>
       <c r="L18" s="58" t="s">
         <v>100</v>
       </c>
@@ -6383,79 +6270,71 @@
       <c r="O18" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="P18" s="120"/>
-      <c r="Q18" s="130"/>
-      <c r="R18" s="115"/>
-      <c r="S18" s="139"/>
-      <c r="T18" s="121">
+      <c r="P18" s="164"/>
+      <c r="Q18" s="165"/>
+      <c r="R18" s="166"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="141">
         <v>2</v>
       </c>
-      <c r="U18" s="122"/>
+      <c r="U18" s="143"/>
       <c r="V18" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="W18" s="138"/>
-    </row>
-    <row r="19" spans="2:23">
-      <c r="B19" s="138"/>
+    </row>
+    <row r="19" spans="3:22">
       <c r="C19" s="41" t="s">
         <v>14</v>
       </c>
       <c r="D19" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="162" t="s">
+      <c r="E19" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="164" t="s">
+      <c r="F19" s="79" t="s">
         <v>81</v>
       </c>
       <c r="G19" s="46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I19" s="45">
         <v>3</v>
       </c>
       <c r="J19" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="K19" s="138"/>
-      <c r="L19" s="138"/>
-      <c r="M19" s="138"/>
+        <v>280</v>
+      </c>
       <c r="N19" s="63"/>
       <c r="O19" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="P19" s="146" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q19" s="147"/>
-      <c r="R19" s="148"/>
-      <c r="S19" s="138"/>
-      <c r="T19" s="121">
+      <c r="P19" s="181" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q19" s="182"/>
+      <c r="R19" s="183"/>
+      <c r="T19" s="141">
         <v>3</v>
       </c>
-      <c r="U19" s="122"/>
+      <c r="U19" s="143"/>
       <c r="V19" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="W19" s="138"/>
-    </row>
-    <row r="20" spans="2:23">
-      <c r="B20" s="138"/>
+    </row>
+    <row r="20" spans="3:22">
       <c r="C20" s="43" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="162" t="s">
+      <c r="E20" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="164" t="s">
+      <c r="F20" s="79" t="s">
         <v>82</v>
       </c>
       <c r="G20" s="46" t="s">
@@ -6468,46 +6347,43 @@
         <v>3</v>
       </c>
       <c r="J20" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="K20" s="138"/>
+        <v>208</v>
+      </c>
       <c r="L20" s="47" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M20" s="47" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N20" s="67"/>
       <c r="O20" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="P20" s="149" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q20" s="150"/>
-      <c r="R20" s="151"/>
-      <c r="S20" s="139"/>
-      <c r="T20" s="121">
+      <c r="P20" s="178" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q20" s="179"/>
+      <c r="R20" s="180"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="141">
         <v>4</v>
       </c>
-      <c r="U20" s="122"/>
+      <c r="U20" s="143"/>
       <c r="V20" s="68" t="s">
-        <v>241</v>
-      </c>
-      <c r="W20" s="138"/>
-    </row>
-    <row r="21" spans="2:23">
-      <c r="B21" s="138"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22">
       <c r="C21" s="41" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="162" t="s">
+      <c r="E21" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="164" t="s">
+      <c r="F21" s="79" t="s">
         <v>83</v>
       </c>
       <c r="G21" s="45" t="s">
@@ -6520,46 +6396,42 @@
         <v>3</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="K21" s="138"/>
+        <v>209</v>
+      </c>
       <c r="L21" s="44" t="s">
         <v>97</v>
       </c>
       <c r="M21" s="43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N21" s="63"/>
       <c r="O21" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="P21" s="152" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q21" s="147"/>
-      <c r="R21" s="148"/>
-      <c r="S21" s="138"/>
-      <c r="T21" s="121">
+      <c r="P21" s="184" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q21" s="182"/>
+      <c r="R21" s="183"/>
+      <c r="T21" s="141">
         <v>5</v>
       </c>
-      <c r="U21" s="122"/>
+      <c r="U21" s="143"/>
       <c r="V21" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="W21" s="138"/>
-    </row>
-    <row r="22" spans="2:23">
-      <c r="B22" s="138"/>
+    </row>
+    <row r="22" spans="3:22">
       <c r="C22" s="43" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="E22" s="162" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="164" t="s">
+      <c r="F22" s="79" t="s">
         <v>84</v>
       </c>
       <c r="G22" s="46" t="s">
@@ -6572,46 +6444,42 @@
         <v>3</v>
       </c>
       <c r="J22" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="K22" s="138"/>
+        <v>210</v>
+      </c>
       <c r="L22" s="57" t="s">
         <v>98</v>
       </c>
       <c r="M22" s="41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="P22" s="152" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q22" s="147"/>
-      <c r="R22" s="148"/>
-      <c r="S22" s="138"/>
-      <c r="T22" s="121">
+      <c r="P22" s="184" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q22" s="182"/>
+      <c r="R22" s="183"/>
+      <c r="T22" s="141">
         <v>6</v>
       </c>
-      <c r="U22" s="122"/>
+      <c r="U22" s="143"/>
       <c r="V22" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="W22" s="138"/>
-    </row>
-    <row r="23" spans="2:23">
-      <c r="B23" s="138"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22">
       <c r="C23" s="41" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="162" t="s">
+      <c r="E23" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="164" t="s">
+      <c r="F23" s="79" t="s">
         <v>85</v>
       </c>
       <c r="G23" s="45" t="s">
@@ -6624,46 +6492,43 @@
         <v>3</v>
       </c>
       <c r="J23" s="41" t="s">
-        <v>213</v>
-      </c>
-      <c r="K23" s="138"/>
+        <v>211</v>
+      </c>
       <c r="L23" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M23" s="43" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N23" s="63"/>
       <c r="O23" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="P23" s="116" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q23" s="117"/>
-      <c r="R23" s="118"/>
-      <c r="S23" s="139"/>
-      <c r="T23" s="121">
+      <c r="P23" s="161" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q23" s="162"/>
+      <c r="R23" s="163"/>
+      <c r="S23" s="69"/>
+      <c r="T23" s="141">
         <v>7</v>
       </c>
-      <c r="U23" s="122"/>
+      <c r="U23" s="143"/>
       <c r="V23" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="W23" s="138"/>
-    </row>
-    <row r="24" spans="2:23">
-      <c r="B24" s="138"/>
+    </row>
+    <row r="24" spans="3:22">
       <c r="C24" s="43" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E24" s="162" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="F24" s="164" t="s">
+      <c r="F24" s="79" t="s">
         <v>82</v>
       </c>
       <c r="G24" s="46" t="s">
@@ -6676,44 +6541,41 @@
         <v>4</v>
       </c>
       <c r="J24" s="43" t="s">
-        <v>214</v>
-      </c>
-      <c r="K24" s="138"/>
+        <v>212</v>
+      </c>
       <c r="L24" s="58" t="s">
         <v>100</v>
       </c>
       <c r="M24" s="42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N24" s="63"/>
       <c r="O24" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="P24" s="119"/>
-      <c r="Q24" s="142"/>
-      <c r="R24" s="114"/>
-      <c r="S24" s="139"/>
-      <c r="T24" s="121">
+      <c r="P24" s="175"/>
+      <c r="Q24" s="176"/>
+      <c r="R24" s="177"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="141">
         <v>8</v>
       </c>
-      <c r="U24" s="122"/>
+      <c r="U24" s="143"/>
       <c r="V24" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="W24" s="138"/>
-    </row>
-    <row r="25" spans="2:23">
-      <c r="B25" s="138"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22">
       <c r="C25" s="41" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="162" t="s">
+      <c r="E25" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="F25" s="164" t="s">
+      <c r="F25" s="79" t="s">
         <v>83</v>
       </c>
       <c r="G25" s="45" t="s">
@@ -6726,40 +6588,35 @@
         <v>3</v>
       </c>
       <c r="J25" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="K25" s="138"/>
-      <c r="L25" s="138"/>
-      <c r="M25" s="138"/>
+        <v>213</v>
+      </c>
       <c r="N25" s="63"/>
       <c r="O25" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="P25" s="120"/>
-      <c r="Q25" s="130"/>
-      <c r="R25" s="115"/>
-      <c r="S25" s="139"/>
-      <c r="T25" s="121">
+      <c r="P25" s="164"/>
+      <c r="Q25" s="165"/>
+      <c r="R25" s="166"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="141">
         <v>9</v>
       </c>
-      <c r="U25" s="122"/>
+      <c r="U25" s="143"/>
       <c r="V25" s="67" t="s">
-        <v>244</v>
-      </c>
-      <c r="W25" s="138"/>
-    </row>
-    <row r="26" spans="2:23">
-      <c r="B26" s="138"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22">
       <c r="C26" s="43" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="162" t="s">
+      <c r="E26" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="F26" s="164" t="s">
+      <c r="F26" s="79" t="s">
         <v>84</v>
       </c>
       <c r="G26" s="46" t="s">
@@ -6772,37 +6629,27 @@
         <v>3</v>
       </c>
       <c r="J26" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="K26" s="138"/>
-      <c r="M26" s="138"/>
-      <c r="N26" s="138"/>
-      <c r="O26" s="138"/>
-      <c r="P26" s="138"/>
-      <c r="Q26" s="138"/>
-      <c r="R26" s="138"/>
-      <c r="S26" s="138"/>
-      <c r="T26" s="121" t="s">
+        <v>214</v>
+      </c>
+      <c r="T26" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="U26" s="122"/>
+      <c r="U26" s="143"/>
       <c r="V26" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="W26" s="138"/>
-    </row>
-    <row r="27" spans="2:23">
-      <c r="B27" s="138"/>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22">
       <c r="C27" s="41" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="162" t="s">
+      <c r="E27" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="164" t="s">
+      <c r="F27" s="79" t="s">
         <v>85</v>
       </c>
       <c r="G27" s="45" t="s">
@@ -6815,39 +6662,35 @@
         <v>3</v>
       </c>
       <c r="J27" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="K27" s="138"/>
-      <c r="L27" s="182" t="s">
-        <v>264</v>
-      </c>
-      <c r="M27" s="180"/>
-      <c r="N27" s="181"/>
-      <c r="P27" s="181"/>
-      <c r="Q27" s="181"/>
-      <c r="R27" s="159"/>
-      <c r="S27" s="138"/>
-      <c r="T27" s="121" t="s">
+        <v>215</v>
+      </c>
+      <c r="L27" s="84" t="s">
+        <v>261</v>
+      </c>
+      <c r="M27" s="83"/>
+      <c r="N27" s="83"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="83"/>
+      <c r="R27" s="74"/>
+      <c r="T27" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="U27" s="122"/>
+      <c r="U27" s="143"/>
       <c r="V27" s="67" t="s">
-        <v>246</v>
-      </c>
-      <c r="W27" s="138"/>
-    </row>
-    <row r="28" spans="2:23">
-      <c r="B28" s="138"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22">
       <c r="C28" s="43" t="s">
         <v>22</v>
       </c>
       <c r="D28" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="162" t="s">
+      <c r="E28" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="F28" s="164" t="s">
+      <c r="F28" s="79" t="s">
         <v>78</v>
       </c>
       <c r="G28" s="46" t="s">
@@ -6860,38 +6703,33 @@
         <v>4</v>
       </c>
       <c r="J28" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="K28" s="138"/>
-      <c r="L28" s="182" t="s">
-        <v>265</v>
-      </c>
-      <c r="M28" s="180"/>
-      <c r="N28" s="181"/>
-      <c r="Q28" s="181"/>
-      <c r="R28" s="138"/>
-      <c r="S28" s="138"/>
-      <c r="T28" s="121" t="s">
+        <v>216</v>
+      </c>
+      <c r="L28" s="84" t="s">
+        <v>262</v>
+      </c>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
+      <c r="Q28" s="83"/>
+      <c r="T28" s="141" t="s">
         <v>118</v>
       </c>
-      <c r="U28" s="122"/>
+      <c r="U28" s="143"/>
       <c r="V28" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="W28" s="138"/>
-    </row>
-    <row r="29" spans="2:23">
-      <c r="B29" s="138"/>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22">
       <c r="C29" s="43" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="162" t="s">
+      <c r="E29" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="F29" s="164" t="s">
+      <c r="F29" s="79" t="s">
         <v>81</v>
       </c>
       <c r="G29" s="46" t="s">
@@ -6904,327 +6742,219 @@
         <v>3</v>
       </c>
       <c r="J29" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="K29" s="138"/>
-      <c r="L29" s="182" t="s">
-        <v>266</v>
-      </c>
-      <c r="M29" s="180"/>
-      <c r="N29" s="181"/>
-      <c r="P29" s="183" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q29" s="181"/>
-      <c r="R29" s="138"/>
-      <c r="S29" s="138"/>
-      <c r="T29" s="116" t="s">
+        <v>217</v>
+      </c>
+      <c r="L29" s="84" t="s">
+        <v>263</v>
+      </c>
+      <c r="M29" s="83"/>
+      <c r="N29" s="83"/>
+      <c r="P29" s="85" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q29" s="83"/>
+      <c r="T29" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="U29" s="118"/>
-      <c r="V29" s="140" t="s">
-        <v>248</v>
-      </c>
-      <c r="W29" s="138"/>
-    </row>
-    <row r="30" spans="2:23">
-      <c r="B30" s="138"/>
+      <c r="U29" s="163"/>
+      <c r="V29" s="155" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22">
       <c r="C30" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="E30" s="77" t="s">
         <v>252</v>
       </c>
-      <c r="D30" s="43" t="s">
+      <c r="F30" s="79" t="s">
         <v>253</v>
       </c>
-      <c r="E30" s="162" t="s">
+      <c r="G30" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="H30" s="50" t="s">
         <v>254</v>
-      </c>
-      <c r="F30" s="164" t="s">
-        <v>255</v>
-      </c>
-      <c r="G30" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="H30" s="50" t="s">
-        <v>256</v>
       </c>
       <c r="I30" s="46">
         <v>3</v>
       </c>
       <c r="J30" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="L30" s="84" t="s">
+        <v>264</v>
+      </c>
+      <c r="M30" s="83"/>
+      <c r="N30" s="83"/>
+      <c r="P30" s="85" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q30" s="83"/>
+      <c r="T30" s="164" t="s">
+        <v>119</v>
+      </c>
+      <c r="U30" s="166"/>
+      <c r="V30" s="156"/>
+    </row>
+    <row r="31" spans="3:22">
+      <c r="C31" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="D31" s="43" t="s">
         <v>257</v>
       </c>
-      <c r="K30" s="138"/>
-      <c r="L30" s="182" t="s">
-        <v>267</v>
-      </c>
-      <c r="M30" s="180"/>
-      <c r="N30" s="181"/>
-      <c r="P30" s="183" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q30" s="181"/>
-      <c r="R30" s="138"/>
-      <c r="S30" s="138"/>
-      <c r="T30" s="120" t="s">
-        <v>119</v>
-      </c>
-      <c r="U30" s="115"/>
-      <c r="V30" s="141"/>
-      <c r="W30" s="138"/>
-    </row>
-    <row r="31" spans="2:23">
-      <c r="B31" s="138"/>
-      <c r="C31" s="43" t="s">
+      <c r="E31" s="77" t="s">
+        <v>252</v>
+      </c>
+      <c r="F31" s="79" t="s">
         <v>258</v>
       </c>
-      <c r="D31" s="43" t="s">
-        <v>259</v>
-      </c>
-      <c r="E31" s="162" t="s">
+      <c r="G31" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="H31" s="50" t="s">
         <v>254</v>
-      </c>
-      <c r="F31" s="164" t="s">
-        <v>260</v>
-      </c>
-      <c r="G31" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>256</v>
       </c>
       <c r="I31" s="46">
         <v>4</v>
       </c>
       <c r="J31" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="K31" s="138"/>
-      <c r="L31" s="183" t="s">
-        <v>268</v>
-      </c>
-      <c r="M31" s="138"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="138"/>
-      <c r="P31" s="183" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q31" s="138"/>
-      <c r="R31" s="138"/>
-      <c r="S31" s="138"/>
-      <c r="T31" s="138"/>
-      <c r="U31" s="138"/>
-      <c r="V31" s="138"/>
-      <c r="W31" s="138"/>
-    </row>
-    <row r="32" spans="2:23">
-      <c r="B32" s="138"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="138"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="138"/>
-      <c r="I32" s="138"/>
-      <c r="J32" s="138"/>
-      <c r="K32" s="138"/>
-      <c r="L32" s="138"/>
-      <c r="M32" s="138"/>
-      <c r="N32" s="138"/>
-      <c r="O32" s="138"/>
-      <c r="P32" s="138"/>
-      <c r="Q32" s="138"/>
-      <c r="R32" s="138"/>
-      <c r="S32" s="138"/>
-      <c r="T32" s="138"/>
-      <c r="U32" s="138"/>
-      <c r="V32" s="138"/>
-      <c r="W32" s="138"/>
+        <v>259</v>
+      </c>
+      <c r="L31" s="85" t="s">
+        <v>265</v>
+      </c>
+      <c r="P31" s="85" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="33" spans="1:24">
-      <c r="A33" s="155"/>
-      <c r="B33" s="156"/>
-      <c r="W33" s="155"/>
-      <c r="X33" s="156"/>
+      <c r="A33" s="70"/>
+      <c r="B33" s="71"/>
+      <c r="W33" s="70"/>
+      <c r="X33" s="71"/>
     </row>
     <row r="34" spans="1:24">
-      <c r="A34" s="157"/>
-      <c r="B34" s="158"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="138"/>
-      <c r="H34" s="138"/>
-      <c r="I34" s="138"/>
-      <c r="J34" s="138"/>
-      <c r="K34" s="138"/>
-      <c r="L34" s="138"/>
-      <c r="M34" s="138"/>
-      <c r="N34" s="138"/>
-      <c r="O34" s="138"/>
-      <c r="P34" s="138"/>
-      <c r="Q34" s="138"/>
-      <c r="R34" s="138"/>
-      <c r="S34" s="138"/>
-      <c r="T34" s="138"/>
-      <c r="U34" s="138"/>
-      <c r="V34" s="138"/>
-      <c r="W34" s="157"/>
-      <c r="X34" s="158"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="73"/>
+      <c r="W34" s="72"/>
+      <c r="X34" s="73"/>
     </row>
     <row r="35" spans="1:24">
-      <c r="A35" s="138"/>
-      <c r="B35" s="138"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="138"/>
-      <c r="I35" s="138"/>
-      <c r="J35" s="145" t="s">
-        <v>250</v>
-      </c>
-      <c r="K35" s="145"/>
-      <c r="L35" s="145"/>
-      <c r="M35" s="145"/>
-      <c r="N35" s="138"/>
-      <c r="O35" s="138"/>
-      <c r="P35" s="138"/>
-      <c r="Q35" s="138"/>
-      <c r="R35" s="138"/>
-      <c r="S35" s="138"/>
-      <c r="T35" s="138"/>
-      <c r="U35" s="138"/>
-      <c r="V35" s="138"/>
-      <c r="W35" s="138"/>
+      <c r="J35" s="138" t="s">
+        <v>248</v>
+      </c>
+      <c r="K35" s="138"/>
+      <c r="L35" s="138"/>
+      <c r="M35" s="138"/>
     </row>
     <row r="36" spans="1:24">
-      <c r="B36" s="138"/>
-      <c r="C36" s="138" t="s">
-        <v>263</v>
-      </c>
-      <c r="D36" s="138"/>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="145"/>
-      <c r="K36" s="145"/>
-      <c r="L36" s="145"/>
-      <c r="M36" s="145"/>
-      <c r="N36" s="138"/>
-      <c r="O36" s="138"/>
-      <c r="P36" s="138"/>
-      <c r="Q36" s="138"/>
-      <c r="R36" s="138"/>
-      <c r="S36" s="138"/>
-      <c r="T36" s="138"/>
-      <c r="U36" s="138"/>
-      <c r="V36" s="138"/>
-      <c r="W36" s="138"/>
+      <c r="C36" t="s">
+        <v>278</v>
+      </c>
+      <c r="J36" s="138"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="138"/>
+      <c r="M36" s="138"/>
     </row>
     <row r="37" spans="1:24">
-      <c r="B37" s="138"/>
       <c r="C37" s="134" t="s">
         <v>189</v>
       </c>
       <c r="D37" s="134" t="s">
         <v>190</v>
       </c>
-      <c r="E37" s="131" t="s">
+      <c r="E37" s="136" t="s">
         <v>191</v>
       </c>
-      <c r="F37" s="133"/>
+      <c r="F37" s="137"/>
       <c r="G37" s="134" t="s">
         <v>192</v>
       </c>
       <c r="H37" s="134" t="s">
         <v>193</v>
       </c>
-      <c r="I37" s="124" t="s">
+      <c r="I37" s="139" t="s">
         <v>187</v>
       </c>
       <c r="J37" s="134" t="s">
         <v>194</v>
       </c>
-      <c r="K37" s="138"/>
       <c r="L37" s="134" t="s">
         <v>189</v>
       </c>
       <c r="M37" s="134" t="s">
         <v>190</v>
       </c>
-      <c r="N37" s="131" t="s">
+      <c r="N37" s="136" t="s">
         <v>191</v>
       </c>
-      <c r="O37" s="132"/>
-      <c r="P37" s="133"/>
+      <c r="O37" s="154"/>
+      <c r="P37" s="137"/>
       <c r="Q37" s="134" t="s">
         <v>192</v>
       </c>
-      <c r="R37" s="124" t="s">
+      <c r="R37" s="139" t="s">
         <v>193</v>
       </c>
-      <c r="S37" s="125"/>
-      <c r="T37" s="126"/>
+      <c r="S37" s="149"/>
+      <c r="T37" s="150"/>
       <c r="U37" s="134" t="s">
         <v>187</v>
       </c>
       <c r="V37" s="134" t="s">
         <v>194</v>
       </c>
-      <c r="W37" s="138"/>
     </row>
     <row r="38" spans="1:24">
-      <c r="B38" s="138"/>
-      <c r="C38" s="136"/>
-      <c r="D38" s="136"/>
-      <c r="E38" s="160" t="s">
+      <c r="C38" s="135"/>
+      <c r="D38" s="135"/>
+      <c r="E38" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="F38" s="161" t="s">
+      <c r="F38" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="137"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="136"/>
-      <c r="M38" s="136"/>
-      <c r="N38" s="166" t="s">
+      <c r="G38" s="135"/>
+      <c r="H38" s="135"/>
+      <c r="I38" s="140"/>
+      <c r="J38" s="135"/>
+      <c r="L38" s="135"/>
+      <c r="M38" s="135"/>
+      <c r="N38" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="O38" s="167"/>
-      <c r="P38" s="161" t="s">
+      <c r="O38" s="147"/>
+      <c r="P38" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="Q38" s="135"/>
-      <c r="R38" s="127"/>
-      <c r="S38" s="128"/>
-      <c r="T38" s="129"/>
-      <c r="U38" s="135"/>
-      <c r="V38" s="135"/>
-      <c r="W38" s="138"/>
+      <c r="Q38" s="148"/>
+      <c r="R38" s="151"/>
+      <c r="S38" s="152"/>
+      <c r="T38" s="153"/>
+      <c r="U38" s="148"/>
+      <c r="V38" s="148"/>
     </row>
     <row r="39" spans="1:24">
-      <c r="B39" s="138"/>
       <c r="C39" s="43" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="E39" s="162" t="s">
+      <c r="E39" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="163" t="s">
+      <c r="F39" s="78" t="s">
         <v>34</v>
       </c>
       <c r="G39" s="49" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H39" s="50" t="s">
         <v>36</v>
@@ -7233,50 +6963,47 @@
         <v>2</v>
       </c>
       <c r="J39" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="K39" s="138"/>
+        <v>199</v>
+      </c>
       <c r="L39" s="55" t="s">
         <v>26</v>
       </c>
       <c r="M39" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="N39" s="168" t="s">
+      <c r="N39" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="O39" s="169"/>
-      <c r="P39" s="170" t="s">
+      <c r="O39" s="145"/>
+      <c r="P39" s="81" t="s">
         <v>34</v>
       </c>
       <c r="Q39" s="61" t="s">
-        <v>249</v>
-      </c>
-      <c r="R39" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R39" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="S39" s="123"/>
-      <c r="T39" s="122"/>
+      <c r="S39" s="142"/>
+      <c r="T39" s="143"/>
       <c r="U39" s="45">
         <v>3</v>
       </c>
       <c r="V39" s="41" t="s">
-        <v>221</v>
-      </c>
-      <c r="W39" s="138"/>
+        <v>219</v>
+      </c>
     </row>
     <row r="40" spans="1:24">
-      <c r="B40" s="138"/>
       <c r="C40" s="41" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="162" t="s">
-        <v>198</v>
-      </c>
-      <c r="F40" s="164" t="s">
+      <c r="E40" s="77" t="s">
+        <v>197</v>
+      </c>
+      <c r="F40" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G40" s="46" t="s">
@@ -7289,50 +7016,47 @@
         <v>4</v>
       </c>
       <c r="J40" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="K40" s="138"/>
+        <v>200</v>
+      </c>
       <c r="L40" s="60" t="s">
         <v>27</v>
       </c>
       <c r="M40" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="N40" s="171" t="s">
+      <c r="N40" s="157" t="s">
         <v>91</v>
       </c>
-      <c r="O40" s="172"/>
-      <c r="P40" s="163" t="s">
+      <c r="O40" s="158"/>
+      <c r="P40" s="78" t="s">
         <v>92</v>
       </c>
       <c r="Q40" s="49" t="s">
-        <v>249</v>
-      </c>
-      <c r="R40" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R40" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="S40" s="123"/>
-      <c r="T40" s="122"/>
+      <c r="S40" s="142"/>
+      <c r="T40" s="143"/>
       <c r="U40" s="46">
         <v>3</v>
       </c>
       <c r="V40" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="W40" s="138"/>
+        <v>220</v>
+      </c>
     </row>
     <row r="41" spans="1:24">
-      <c r="B41" s="138"/>
       <c r="C41" s="43" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="162" t="s">
+      <c r="E41" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="F41" s="165" t="s">
+      <c r="F41" s="80" t="s">
         <v>66</v>
       </c>
       <c r="G41" s="45" t="s">
@@ -7345,153 +7069,144 @@
         <v>3</v>
       </c>
       <c r="J41" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="K41" s="138"/>
+        <v>279</v>
+      </c>
       <c r="L41" s="55" t="s">
         <v>28</v>
       </c>
       <c r="M41" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="N41" s="168" t="s">
+      <c r="N41" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="O41" s="169"/>
-      <c r="P41" s="170" t="s">
+      <c r="O41" s="145"/>
+      <c r="P41" s="81" t="s">
         <v>93</v>
       </c>
       <c r="Q41" s="61" t="s">
-        <v>249</v>
-      </c>
-      <c r="R41" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R41" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="S41" s="123"/>
-      <c r="T41" s="122"/>
+      <c r="S41" s="142"/>
+      <c r="T41" s="143"/>
       <c r="U41" s="45">
         <v>3</v>
       </c>
       <c r="V41" s="41" t="s">
-        <v>223</v>
-      </c>
-      <c r="W41" s="138"/>
+        <v>221</v>
+      </c>
     </row>
     <row r="42" spans="1:24">
-      <c r="B42" s="138"/>
       <c r="C42" s="41" t="s">
         <v>5</v>
       </c>
       <c r="D42" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E42" s="162" t="s">
+      <c r="E42" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="F42" s="164" t="s">
+      <c r="F42" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G42" s="46" t="s">
         <v>35</v>
       </c>
       <c r="H42" s="46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I42" s="45">
         <v>4</v>
       </c>
       <c r="J42" s="42" t="s">
-        <v>203</v>
-      </c>
-      <c r="K42" s="138"/>
-      <c r="L42" s="140" t="s">
+        <v>201</v>
+      </c>
+      <c r="L42" s="155" t="s">
         <v>29</v>
       </c>
-      <c r="M42" s="140" t="s">
-        <v>220</v>
-      </c>
-      <c r="N42" s="173" t="s">
+      <c r="M42" s="155" t="s">
+        <v>218</v>
+      </c>
+      <c r="N42" s="171" t="s">
         <v>91</v>
       </c>
-      <c r="O42" s="174"/>
-      <c r="P42" s="175" t="s">
+      <c r="O42" s="172"/>
+      <c r="P42" s="169" t="s">
         <v>89</v>
       </c>
-      <c r="Q42" s="143" t="s">
-        <v>249</v>
-      </c>
-      <c r="R42" s="116" t="s">
-        <v>36</v>
-      </c>
-      <c r="S42" s="117"/>
-      <c r="T42" s="118"/>
-      <c r="U42" s="140">
+      <c r="Q42" s="167" t="s">
+        <v>247</v>
+      </c>
+      <c r="R42" s="161" t="s">
+        <v>281</v>
+      </c>
+      <c r="S42" s="162"/>
+      <c r="T42" s="163"/>
+      <c r="U42" s="155">
         <v>4</v>
       </c>
-      <c r="V42" s="153" t="s">
-        <v>262</v>
-      </c>
-      <c r="W42" s="138"/>
+      <c r="V42" s="159" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="43" spans="1:24">
-      <c r="B43" s="138"/>
       <c r="C43" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D43" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="E43" s="162" t="s">
+      <c r="E43" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="F43" s="165" t="s">
+      <c r="F43" s="80" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="45" t="s">
         <v>35</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I43" s="46">
         <v>4</v>
       </c>
       <c r="J43" s="42" t="s">
-        <v>204</v>
-      </c>
-      <c r="K43" s="138"/>
-      <c r="L43" s="141"/>
-      <c r="M43" s="141"/>
-      <c r="N43" s="176"/>
-      <c r="O43" s="177"/>
-      <c r="P43" s="178"/>
-      <c r="Q43" s="144"/>
-      <c r="R43" s="120"/>
-      <c r="S43" s="130"/>
-      <c r="T43" s="115"/>
-      <c r="U43" s="141"/>
-      <c r="V43" s="154"/>
-      <c r="W43" s="138"/>
+        <v>202</v>
+      </c>
+      <c r="L43" s="156"/>
+      <c r="M43" s="156"/>
+      <c r="N43" s="173"/>
+      <c r="O43" s="174"/>
+      <c r="P43" s="170"/>
+      <c r="Q43" s="168"/>
+      <c r="R43" s="164"/>
+      <c r="S43" s="165"/>
+      <c r="T43" s="166"/>
+      <c r="U43" s="156"/>
+      <c r="V43" s="160"/>
     </row>
     <row r="44" spans="1:24">
-      <c r="B44" s="138"/>
       <c r="C44" s="41" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="162" t="s">
+      <c r="E44" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="F44" s="164" t="s">
+      <c r="F44" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G44" s="46" t="s">
         <v>35</v>
       </c>
       <c r="H44" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I44" s="46">
         <v>4</v>
@@ -7499,151 +7214,130 @@
       <c r="J44" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="K44" s="138"/>
       <c r="L44" s="56" t="s">
         <v>30</v>
       </c>
       <c r="M44" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="N44" s="168" t="s">
+      <c r="N44" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="O44" s="169"/>
-      <c r="P44" s="179" t="s">
+      <c r="O44" s="145"/>
+      <c r="P44" s="82" t="s">
         <v>89</v>
       </c>
       <c r="Q44" s="59" t="s">
-        <v>249</v>
-      </c>
-      <c r="R44" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R44" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="S44" s="123"/>
-      <c r="T44" s="122"/>
+      <c r="S44" s="142"/>
+      <c r="T44" s="143"/>
       <c r="U44" s="48">
         <v>3</v>
       </c>
       <c r="V44" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="W44" s="138"/>
+        <v>222</v>
+      </c>
     </row>
     <row r="45" spans="1:24">
-      <c r="B45" s="138"/>
       <c r="C45" s="43" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="E45" s="162" t="s">
+      <c r="E45" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="F45" s="164" t="s">
+      <c r="F45" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G45" s="45" t="s">
         <v>35</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I45" s="46">
         <v>4</v>
       </c>
       <c r="J45" s="52" t="s">
-        <v>205</v>
-      </c>
-      <c r="K45" s="138"/>
-      <c r="L45" s="138"/>
-      <c r="M45" s="138"/>
-      <c r="N45" s="138"/>
-      <c r="O45" s="138"/>
-      <c r="P45" s="138"/>
-      <c r="Q45" s="138"/>
-      <c r="R45" s="138"/>
-      <c r="S45" s="138"/>
-      <c r="T45" s="138"/>
-      <c r="U45" s="138"/>
-      <c r="V45" s="138"/>
-      <c r="W45" s="138"/>
+        <v>203</v>
+      </c>
     </row>
     <row r="46" spans="1:24">
-      <c r="B46" s="138"/>
       <c r="C46" s="41" t="s">
         <v>9</v>
       </c>
       <c r="D46" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E46" s="162" t="s">
+      <c r="E46" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="F46" s="165" t="s">
+      <c r="F46" s="80" t="s">
         <v>66</v>
       </c>
       <c r="G46" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="H46" s="139" t="s">
-        <v>199</v>
+      <c r="H46" s="69" t="s">
+        <v>198</v>
       </c>
       <c r="I46" s="45">
         <v>4</v>
       </c>
       <c r="J46" s="52" t="s">
-        <v>206</v>
-      </c>
-      <c r="K46" s="138"/>
+        <v>204</v>
+      </c>
       <c r="L46" s="46" t="s">
         <v>69</v>
       </c>
       <c r="M46" s="65" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N46" s="67"/>
-      <c r="O46" s="121" t="s">
-        <v>231</v>
-      </c>
-      <c r="P46" s="123"/>
-      <c r="Q46" s="123"/>
-      <c r="R46" s="122"/>
-      <c r="S46" s="139"/>
-      <c r="T46" s="121" t="s">
-        <v>238</v>
-      </c>
-      <c r="U46" s="123"/>
-      <c r="V46" s="122"/>
-      <c r="W46" s="138"/>
+      <c r="O46" s="141" t="s">
+        <v>229</v>
+      </c>
+      <c r="P46" s="142"/>
+      <c r="Q46" s="142"/>
+      <c r="R46" s="143"/>
+      <c r="S46" s="69"/>
+      <c r="T46" s="141" t="s">
+        <v>236</v>
+      </c>
+      <c r="U46" s="142"/>
+      <c r="V46" s="143"/>
     </row>
     <row r="47" spans="1:24">
-      <c r="B47" s="138"/>
       <c r="C47" s="43" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="E47" s="162" t="s">
+      <c r="E47" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="F47" s="164" t="s">
+      <c r="F47" s="79" t="s">
         <v>66</v>
       </c>
       <c r="G47" s="46" t="s">
         <v>35</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I47" s="46">
         <v>4</v>
       </c>
       <c r="J47" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="K47" s="138"/>
+        <v>205</v>
+      </c>
       <c r="L47" s="44" t="s">
         <v>97</v>
       </c>
@@ -7654,48 +7348,45 @@
       <c r="O47" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="P47" s="121" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q47" s="123"/>
-      <c r="R47" s="122"/>
-      <c r="S47" s="139"/>
-      <c r="T47" s="121" t="s">
+      <c r="P47" s="141" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q47" s="142"/>
+      <c r="R47" s="143"/>
+      <c r="S47" s="69"/>
+      <c r="T47" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="U47" s="122"/>
+      <c r="U47" s="143"/>
       <c r="V47" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="W47" s="138"/>
     </row>
     <row r="48" spans="1:24">
-      <c r="B48" s="138"/>
       <c r="C48" s="43" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="E48" s="162" t="s">
+      <c r="E48" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F48" s="164" t="s">
+      <c r="F48" s="79" t="s">
         <v>78</v>
       </c>
       <c r="G48" s="46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H48" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I48" s="46">
         <v>3</v>
       </c>
       <c r="J48" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="K48" s="138"/>
+        <v>206</v>
+      </c>
       <c r="L48" s="57" t="s">
         <v>98</v>
       </c>
@@ -7706,48 +7397,45 @@
       <c r="O48" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="P48" s="116" t="s">
+      <c r="P48" s="161" t="s">
         <v>114</v>
       </c>
-      <c r="Q48" s="117"/>
-      <c r="R48" s="118"/>
-      <c r="S48" s="139"/>
-      <c r="T48" s="121">
+      <c r="Q48" s="162"/>
+      <c r="R48" s="163"/>
+      <c r="S48" s="69"/>
+      <c r="T48" s="141">
         <v>0</v>
       </c>
-      <c r="U48" s="122"/>
+      <c r="U48" s="143"/>
       <c r="V48" s="46" t="s">
-        <v>239</v>
-      </c>
-      <c r="W48" s="138"/>
-    </row>
-    <row r="49" spans="2:23">
-      <c r="B49" s="138"/>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22">
       <c r="C49" s="41" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="E49" s="162" t="s">
+      <c r="E49" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F49" s="164" t="s">
+      <c r="F49" s="79" t="s">
         <v>79</v>
       </c>
       <c r="G49" s="46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I49" s="45">
         <v>3</v>
       </c>
       <c r="J49" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="K49" s="138"/>
+        <v>206</v>
+      </c>
       <c r="L49" s="44" t="s">
         <v>99</v>
       </c>
@@ -7758,46 +7446,43 @@
       <c r="O49" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="P49" s="119"/>
-      <c r="Q49" s="142"/>
-      <c r="R49" s="114"/>
-      <c r="S49" s="139"/>
-      <c r="T49" s="121">
+      <c r="P49" s="175"/>
+      <c r="Q49" s="176"/>
+      <c r="R49" s="177"/>
+      <c r="S49" s="69"/>
+      <c r="T49" s="141">
         <v>1</v>
       </c>
-      <c r="U49" s="122"/>
+      <c r="U49" s="143"/>
       <c r="V49" s="67" t="s">
-        <v>240</v>
-      </c>
-      <c r="W49" s="138"/>
-    </row>
-    <row r="50" spans="2:23">
-      <c r="B50" s="138"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22">
       <c r="C50" s="43" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="E50" s="162" t="s">
+      <c r="E50" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="164" t="s">
+      <c r="F50" s="79" t="s">
         <v>80</v>
       </c>
       <c r="G50" s="46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H50" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I50" s="46">
         <v>3</v>
       </c>
       <c r="J50" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="K50" s="138"/>
+        <v>207</v>
+      </c>
       <c r="L50" s="58" t="s">
         <v>100</v>
       </c>
@@ -7808,79 +7493,71 @@
       <c r="O50" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="P50" s="120"/>
-      <c r="Q50" s="130"/>
-      <c r="R50" s="115"/>
-      <c r="S50" s="139"/>
-      <c r="T50" s="121">
+      <c r="P50" s="164"/>
+      <c r="Q50" s="165"/>
+      <c r="R50" s="166"/>
+      <c r="S50" s="69"/>
+      <c r="T50" s="141">
         <v>2</v>
       </c>
-      <c r="U50" s="122"/>
+      <c r="U50" s="143"/>
       <c r="V50" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="W50" s="138"/>
-    </row>
-    <row r="51" spans="2:23">
-      <c r="B51" s="138"/>
+    </row>
+    <row r="51" spans="3:22">
       <c r="C51" s="41" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E51" s="162" t="s">
+      <c r="E51" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F51" s="164" t="s">
+      <c r="F51" s="79" t="s">
         <v>81</v>
       </c>
       <c r="G51" s="46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I51" s="45">
         <v>3</v>
       </c>
       <c r="J51" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="K51" s="138"/>
-      <c r="L51" s="138"/>
-      <c r="M51" s="138"/>
+        <v>280</v>
+      </c>
       <c r="N51" s="63"/>
       <c r="O51" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="P51" s="146" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q51" s="147"/>
-      <c r="R51" s="148"/>
-      <c r="S51" s="138"/>
-      <c r="T51" s="121">
+      <c r="P51" s="181" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q51" s="182"/>
+      <c r="R51" s="183"/>
+      <c r="T51" s="141">
         <v>3</v>
       </c>
-      <c r="U51" s="122"/>
+      <c r="U51" s="143"/>
       <c r="V51" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="W51" s="138"/>
-    </row>
-    <row r="52" spans="2:23">
-      <c r="B52" s="138"/>
+    </row>
+    <row r="52" spans="3:22">
       <c r="C52" s="43" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="E52" s="162" t="s">
+      <c r="E52" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F52" s="164" t="s">
+      <c r="F52" s="79" t="s">
         <v>82</v>
       </c>
       <c r="G52" s="46" t="s">
@@ -7893,46 +7570,43 @@
         <v>3</v>
       </c>
       <c r="J52" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="K52" s="138"/>
+        <v>208</v>
+      </c>
       <c r="L52" s="47" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M52" s="47" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N52" s="67"/>
       <c r="O52" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="P52" s="149" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q52" s="150"/>
-      <c r="R52" s="151"/>
-      <c r="S52" s="139"/>
-      <c r="T52" s="121">
+      <c r="P52" s="178" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q52" s="179"/>
+      <c r="R52" s="180"/>
+      <c r="S52" s="69"/>
+      <c r="T52" s="141">
         <v>4</v>
       </c>
-      <c r="U52" s="122"/>
+      <c r="U52" s="143"/>
       <c r="V52" s="68" t="s">
-        <v>241</v>
-      </c>
-      <c r="W52" s="138"/>
-    </row>
-    <row r="53" spans="2:23">
-      <c r="B53" s="138"/>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22">
       <c r="C53" s="41" t="s">
         <v>16</v>
       </c>
       <c r="D53" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="E53" s="162" t="s">
+      <c r="E53" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F53" s="164" t="s">
+      <c r="F53" s="79" t="s">
         <v>83</v>
       </c>
       <c r="G53" s="45" t="s">
@@ -7945,46 +7619,42 @@
         <v>3</v>
       </c>
       <c r="J53" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="K53" s="138"/>
+        <v>209</v>
+      </c>
       <c r="L53" s="44" t="s">
         <v>97</v>
       </c>
       <c r="M53" s="43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N53" s="63"/>
       <c r="O53" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="P53" s="152" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q53" s="147"/>
-      <c r="R53" s="148"/>
-      <c r="S53" s="138"/>
-      <c r="T53" s="121">
+      <c r="P53" s="184" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q53" s="182"/>
+      <c r="R53" s="183"/>
+      <c r="T53" s="141">
         <v>5</v>
       </c>
-      <c r="U53" s="122"/>
+      <c r="U53" s="143"/>
       <c r="V53" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="W53" s="138"/>
-    </row>
-    <row r="54" spans="2:23">
-      <c r="B54" s="138"/>
+    </row>
+    <row r="54" spans="3:22">
       <c r="C54" s="43" t="s">
         <v>17</v>
       </c>
       <c r="D54" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="E54" s="162" t="s">
+        <v>50</v>
+      </c>
+      <c r="E54" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F54" s="164" t="s">
+      <c r="F54" s="79" t="s">
         <v>84</v>
       </c>
       <c r="G54" s="46" t="s">
@@ -7997,46 +7667,42 @@
         <v>3</v>
       </c>
       <c r="J54" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="K54" s="138"/>
+        <v>210</v>
+      </c>
       <c r="L54" s="57" t="s">
         <v>98</v>
       </c>
       <c r="M54" s="41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N54" s="63"/>
       <c r="O54" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="P54" s="152" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q54" s="147"/>
-      <c r="R54" s="148"/>
-      <c r="S54" s="138"/>
-      <c r="T54" s="121">
+      <c r="P54" s="184" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q54" s="182"/>
+      <c r="R54" s="183"/>
+      <c r="T54" s="141">
         <v>6</v>
       </c>
-      <c r="U54" s="122"/>
+      <c r="U54" s="143"/>
       <c r="V54" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="W54" s="138"/>
-    </row>
-    <row r="55" spans="2:23">
-      <c r="B55" s="138"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22">
       <c r="C55" s="41" t="s">
         <v>96</v>
       </c>
       <c r="D55" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="E55" s="162" t="s">
+      <c r="E55" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="F55" s="164" t="s">
+      <c r="F55" s="79" t="s">
         <v>85</v>
       </c>
       <c r="G55" s="45" t="s">
@@ -8049,46 +7715,43 @@
         <v>3</v>
       </c>
       <c r="J55" s="41" t="s">
-        <v>213</v>
-      </c>
-      <c r="K55" s="138"/>
+        <v>211</v>
+      </c>
       <c r="L55" s="44" t="s">
         <v>99</v>
       </c>
       <c r="M55" s="43" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N55" s="63"/>
       <c r="O55" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="P55" s="116" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q55" s="117"/>
-      <c r="R55" s="118"/>
-      <c r="S55" s="139"/>
-      <c r="T55" s="121">
+      <c r="P55" s="161" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q55" s="162"/>
+      <c r="R55" s="163"/>
+      <c r="S55" s="69"/>
+      <c r="T55" s="141">
         <v>7</v>
       </c>
-      <c r="U55" s="122"/>
+      <c r="U55" s="143"/>
       <c r="V55" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="W55" s="138"/>
-    </row>
-    <row r="56" spans="2:23">
-      <c r="B56" s="138"/>
+    </row>
+    <row r="56" spans="3:22">
       <c r="C56" s="43" t="s">
         <v>18</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E56" s="162" t="s">
+        <v>196</v>
+      </c>
+      <c r="E56" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="F56" s="164" t="s">
+      <c r="F56" s="79" t="s">
         <v>82</v>
       </c>
       <c r="G56" s="46" t="s">
@@ -8101,44 +7764,41 @@
         <v>4</v>
       </c>
       <c r="J56" s="43" t="s">
-        <v>214</v>
-      </c>
-      <c r="K56" s="138"/>
+        <v>212</v>
+      </c>
       <c r="L56" s="58" t="s">
         <v>100</v>
       </c>
       <c r="M56" s="42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N56" s="63"/>
       <c r="O56" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="P56" s="119"/>
-      <c r="Q56" s="142"/>
-      <c r="R56" s="114"/>
-      <c r="S56" s="139"/>
-      <c r="T56" s="121">
+      <c r="P56" s="175"/>
+      <c r="Q56" s="176"/>
+      <c r="R56" s="177"/>
+      <c r="S56" s="69"/>
+      <c r="T56" s="141">
         <v>8</v>
       </c>
-      <c r="U56" s="122"/>
+      <c r="U56" s="143"/>
       <c r="V56" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="W56" s="138"/>
-    </row>
-    <row r="57" spans="2:23">
-      <c r="B57" s="138"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="3:22">
       <c r="C57" s="41" t="s">
         <v>19</v>
       </c>
       <c r="D57" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="E57" s="162" t="s">
+      <c r="E57" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="F57" s="164" t="s">
+      <c r="F57" s="79" t="s">
         <v>83</v>
       </c>
       <c r="G57" s="45" t="s">
@@ -8151,40 +7811,35 @@
         <v>3</v>
       </c>
       <c r="J57" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="K57" s="138"/>
-      <c r="L57" s="138"/>
-      <c r="M57" s="138"/>
+        <v>213</v>
+      </c>
       <c r="N57" s="63"/>
       <c r="O57" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="P57" s="120"/>
-      <c r="Q57" s="130"/>
-      <c r="R57" s="115"/>
-      <c r="S57" s="139"/>
-      <c r="T57" s="121">
+      <c r="P57" s="164"/>
+      <c r="Q57" s="165"/>
+      <c r="R57" s="166"/>
+      <c r="S57" s="69"/>
+      <c r="T57" s="141">
         <v>9</v>
       </c>
-      <c r="U57" s="122"/>
+      <c r="U57" s="143"/>
       <c r="V57" s="67" t="s">
-        <v>244</v>
-      </c>
-      <c r="W57" s="138"/>
-    </row>
-    <row r="58" spans="2:23">
-      <c r="B58" s="138"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22">
       <c r="C58" s="43" t="s">
         <v>20</v>
       </c>
       <c r="D58" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="E58" s="162" t="s">
+      <c r="E58" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="F58" s="164" t="s">
+      <c r="F58" s="79" t="s">
         <v>84</v>
       </c>
       <c r="G58" s="46" t="s">
@@ -8197,38 +7852,27 @@
         <v>3</v>
       </c>
       <c r="J58" s="54" t="s">
-        <v>216</v>
-      </c>
-      <c r="K58" s="138"/>
-      <c r="L58" s="138"/>
-      <c r="M58" s="138"/>
-      <c r="N58" s="138"/>
-      <c r="O58" s="138"/>
-      <c r="P58" s="138"/>
-      <c r="Q58" s="138"/>
-      <c r="R58" s="138"/>
-      <c r="S58" s="138"/>
-      <c r="T58" s="121" t="s">
+        <v>214</v>
+      </c>
+      <c r="T58" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="U58" s="122"/>
+      <c r="U58" s="143"/>
       <c r="V58" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="W58" s="138"/>
-    </row>
-    <row r="59" spans="2:23">
-      <c r="B59" s="138"/>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22">
       <c r="C59" s="41" t="s">
         <v>21</v>
       </c>
       <c r="D59" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="E59" s="162" t="s">
+      <c r="E59" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="F59" s="164" t="s">
+      <c r="F59" s="79" t="s">
         <v>85</v>
       </c>
       <c r="G59" s="45" t="s">
@@ -8241,39 +7885,34 @@
         <v>3</v>
       </c>
       <c r="J59" s="53" t="s">
-        <v>217</v>
-      </c>
-      <c r="K59" s="138"/>
-      <c r="L59" s="182" t="s">
-        <v>264</v>
-      </c>
-      <c r="M59" s="180"/>
-      <c r="N59" s="181"/>
-      <c r="P59" s="181"/>
-      <c r="Q59" s="159"/>
-      <c r="R59" s="138"/>
-      <c r="S59" s="138"/>
-      <c r="T59" s="121" t="s">
+        <v>215</v>
+      </c>
+      <c r="L59" s="84" t="s">
+        <v>261</v>
+      </c>
+      <c r="M59" s="83"/>
+      <c r="N59" s="83"/>
+      <c r="P59" s="83"/>
+      <c r="Q59" s="74"/>
+      <c r="T59" s="141" t="s">
         <v>117</v>
       </c>
-      <c r="U59" s="122"/>
+      <c r="U59" s="143"/>
       <c r="V59" s="67" t="s">
-        <v>246</v>
-      </c>
-      <c r="W59" s="138"/>
-    </row>
-    <row r="60" spans="2:23">
-      <c r="B60" s="138"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22">
       <c r="C60" s="43" t="s">
         <v>22</v>
       </c>
       <c r="D60" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="E60" s="162" t="s">
+      <c r="E60" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="F60" s="164" t="s">
+      <c r="F60" s="79" t="s">
         <v>78</v>
       </c>
       <c r="G60" s="46" t="s">
@@ -8286,38 +7925,33 @@
         <v>4</v>
       </c>
       <c r="J60" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="K60" s="138"/>
-      <c r="L60" s="182" t="s">
-        <v>265</v>
-      </c>
-      <c r="M60" s="180"/>
-      <c r="N60" s="181"/>
-      <c r="Q60" s="159"/>
-      <c r="R60" s="138"/>
-      <c r="S60" s="138"/>
-      <c r="T60" s="121" t="s">
+        <v>216</v>
+      </c>
+      <c r="L60" s="84" t="s">
+        <v>262</v>
+      </c>
+      <c r="M60" s="83"/>
+      <c r="N60" s="83"/>
+      <c r="Q60" s="74"/>
+      <c r="T60" s="141" t="s">
         <v>118</v>
       </c>
-      <c r="U60" s="122"/>
+      <c r="U60" s="143"/>
       <c r="V60" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="W60" s="138"/>
-    </row>
-    <row r="61" spans="2:23">
-      <c r="B61" s="138"/>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22">
       <c r="C61" s="43" t="s">
         <v>23</v>
       </c>
       <c r="D61" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="E61" s="162" t="s">
+      <c r="E61" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="F61" s="164" t="s">
+      <c r="F61" s="79" t="s">
         <v>81</v>
       </c>
       <c r="G61" s="46" t="s">
@@ -8330,220 +7964,163 @@
         <v>3</v>
       </c>
       <c r="J61" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="K61" s="138"/>
-      <c r="L61" s="182" t="s">
-        <v>266</v>
-      </c>
-      <c r="M61" s="180"/>
-      <c r="N61" s="181"/>
-      <c r="P61" s="183" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q61" s="159"/>
-      <c r="R61" s="138"/>
-      <c r="S61" s="138"/>
-      <c r="T61" s="116" t="s">
+        <v>217</v>
+      </c>
+      <c r="L61" s="84" t="s">
+        <v>263</v>
+      </c>
+      <c r="M61" s="83"/>
+      <c r="N61" s="83"/>
+      <c r="P61" s="85" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q61" s="74"/>
+      <c r="T61" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="U61" s="118"/>
-      <c r="V61" s="140" t="s">
-        <v>248</v>
-      </c>
-      <c r="W61" s="138"/>
-    </row>
-    <row r="62" spans="2:23">
-      <c r="B62" s="138"/>
+      <c r="U61" s="163"/>
+      <c r="V61" s="155" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22">
       <c r="C62" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="D62" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="E62" s="77" t="s">
         <v>252</v>
       </c>
-      <c r="D62" s="43" t="s">
+      <c r="F62" s="79" t="s">
         <v>253</v>
       </c>
-      <c r="E62" s="162" t="s">
+      <c r="G62" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="H62" s="50" t="s">
         <v>254</v>
-      </c>
-      <c r="F62" s="164" t="s">
-        <v>255</v>
-      </c>
-      <c r="G62" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="H62" s="50" t="s">
-        <v>256</v>
       </c>
       <c r="I62" s="46">
         <v>3</v>
       </c>
       <c r="J62" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="L62" s="84" t="s">
+        <v>264</v>
+      </c>
+      <c r="M62" s="83"/>
+      <c r="N62" s="83"/>
+      <c r="P62" s="85" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q62" s="74"/>
+      <c r="T62" s="164" t="s">
+        <v>119</v>
+      </c>
+      <c r="U62" s="166"/>
+      <c r="V62" s="156"/>
+    </row>
+    <row r="63" spans="3:22">
+      <c r="C63" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="D63" s="43" t="s">
         <v>257</v>
       </c>
-      <c r="K62" s="138"/>
-      <c r="L62" s="182" t="s">
-        <v>267</v>
-      </c>
-      <c r="M62" s="180"/>
-      <c r="N62" s="181"/>
-      <c r="P62" s="183" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q62" s="159"/>
-      <c r="R62" s="138"/>
-      <c r="S62" s="138"/>
-      <c r="T62" s="120" t="s">
-        <v>119</v>
-      </c>
-      <c r="U62" s="115"/>
-      <c r="V62" s="141"/>
-      <c r="W62" s="138"/>
-    </row>
-    <row r="63" spans="2:23">
-      <c r="B63" s="138"/>
-      <c r="C63" s="43" t="s">
+      <c r="E63" s="77" t="s">
+        <v>252</v>
+      </c>
+      <c r="F63" s="79" t="s">
         <v>258</v>
       </c>
-      <c r="D63" s="43" t="s">
-        <v>259</v>
-      </c>
-      <c r="E63" s="162" t="s">
+      <c r="G63" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="H63" s="50" t="s">
         <v>254</v>
-      </c>
-      <c r="F63" s="164" t="s">
-        <v>260</v>
-      </c>
-      <c r="G63" s="46" t="s">
-        <v>251</v>
-      </c>
-      <c r="H63" s="50" t="s">
-        <v>256</v>
       </c>
       <c r="I63" s="46">
         <v>4</v>
       </c>
       <c r="J63" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="K63" s="138"/>
-      <c r="L63" s="183" t="s">
-        <v>268</v>
-      </c>
-      <c r="M63" s="138"/>
-      <c r="N63" s="138"/>
-      <c r="O63" s="138"/>
-      <c r="P63" s="183" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q63" s="138"/>
-      <c r="R63" s="138"/>
-      <c r="S63" s="138"/>
-      <c r="T63" s="138"/>
-      <c r="U63" s="138"/>
-      <c r="V63" s="138"/>
-      <c r="W63" s="138"/>
-    </row>
-    <row r="64" spans="2:23">
-      <c r="B64" s="138"/>
-      <c r="C64" s="138"/>
-      <c r="D64" s="138"/>
-      <c r="E64" s="138"/>
-      <c r="F64" s="138"/>
-      <c r="G64" s="138"/>
-      <c r="H64" s="138"/>
-      <c r="I64" s="138"/>
-      <c r="J64" s="138"/>
-      <c r="K64" s="138"/>
-      <c r="L64" s="138"/>
-      <c r="M64" s="138"/>
-      <c r="N64" s="138"/>
-      <c r="O64" s="138"/>
-      <c r="P64" s="138"/>
-      <c r="Q64" s="138"/>
-      <c r="R64" s="138"/>
-      <c r="S64" s="138"/>
-      <c r="T64" s="138"/>
-      <c r="U64" s="138"/>
-      <c r="V64" s="138"/>
-      <c r="W64" s="138"/>
+        <v>259</v>
+      </c>
+      <c r="L63" s="85" t="s">
+        <v>265</v>
+      </c>
+      <c r="P63" s="85" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="65" spans="1:24">
-      <c r="A65" s="155"/>
-      <c r="B65" s="156"/>
-      <c r="C65" s="138"/>
-      <c r="D65" s="138"/>
-      <c r="E65" s="138"/>
-      <c r="F65" s="138"/>
-      <c r="G65" s="138"/>
-      <c r="H65" s="138"/>
-      <c r="I65" s="138"/>
-      <c r="J65" s="138"/>
-      <c r="K65" s="138"/>
-      <c r="L65" s="138"/>
-      <c r="M65" s="138"/>
-      <c r="N65" s="138"/>
-      <c r="O65" s="138"/>
-      <c r="P65" s="138"/>
-      <c r="Q65" s="138"/>
-      <c r="R65" s="138"/>
-      <c r="S65" s="138"/>
-      <c r="T65" s="138"/>
-      <c r="U65" s="138"/>
-      <c r="V65" s="138"/>
-      <c r="W65" s="155"/>
-      <c r="X65" s="156"/>
+      <c r="A65" s="70"/>
+      <c r="B65" s="71"/>
+      <c r="W65" s="70"/>
+      <c r="X65" s="71"/>
     </row>
     <row r="66" spans="1:24">
-      <c r="A66" s="157"/>
-      <c r="B66" s="158"/>
-      <c r="W66" s="157"/>
-      <c r="X66" s="158"/>
+      <c r="A66" s="72"/>
+      <c r="B66" s="73"/>
+      <c r="W66" s="72"/>
+      <c r="X66" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="116">
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="J35:M36"/>
-    <mergeCell ref="M37:M38"/>
-    <mergeCell ref="L37:L38"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="V37:V38"/>
-    <mergeCell ref="U37:U38"/>
-    <mergeCell ref="R37:T38"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="M42:M43"/>
-    <mergeCell ref="L42:L43"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="T46:V46"/>
-    <mergeCell ref="O46:R46"/>
-    <mergeCell ref="R44:T44"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="V42:V43"/>
-    <mergeCell ref="U42:U43"/>
-    <mergeCell ref="R42:T43"/>
-    <mergeCell ref="Q42:Q43"/>
-    <mergeCell ref="P42:P43"/>
-    <mergeCell ref="N42:O43"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="P48:R50"/>
-    <mergeCell ref="T47:U47"/>
-    <mergeCell ref="P47:R47"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="P52:R52"/>
-    <mergeCell ref="T51:U51"/>
-    <mergeCell ref="P51:R51"/>
-    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="J3:M4"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="R10:T11"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="R5:T6"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="P16:R18"/>
+    <mergeCell ref="P22:R22"/>
+    <mergeCell ref="P23:R25"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="P21:R21"/>
     <mergeCell ref="P55:R57"/>
     <mergeCell ref="T54:U54"/>
     <mergeCell ref="P54:R54"/>
@@ -8560,62 +8137,54 @@
     <mergeCell ref="T57:U57"/>
     <mergeCell ref="T56:U56"/>
     <mergeCell ref="T55:U55"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="N10:O11"/>
-    <mergeCell ref="P10:P11"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="P16:R18"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="P23:R25"/>
     <mergeCell ref="V29:V30"/>
     <mergeCell ref="T30:U30"/>
     <mergeCell ref="T14:V14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="R10:T11"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="P21:R21"/>
     <mergeCell ref="T25:U25"/>
-    <mergeCell ref="R5:T6"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="R7:T7"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="J3:M4"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="P48:R50"/>
+    <mergeCell ref="T47:U47"/>
+    <mergeCell ref="P47:R47"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="P52:R52"/>
+    <mergeCell ref="T51:U51"/>
+    <mergeCell ref="P51:R51"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="L42:L43"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="T46:V46"/>
+    <mergeCell ref="O46:R46"/>
+    <mergeCell ref="R44:T44"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="V42:V43"/>
+    <mergeCell ref="U42:U43"/>
+    <mergeCell ref="R42:T43"/>
+    <mergeCell ref="Q42:Q43"/>
+    <mergeCell ref="P42:P43"/>
+    <mergeCell ref="N42:O43"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="V37:V38"/>
+    <mergeCell ref="U37:U38"/>
+    <mergeCell ref="R37:T38"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="M42:M43"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="J35:M36"/>
+    <mergeCell ref="M37:M38"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="H37:H38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
